--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130302398</v>
+        <v>130301089</v>
       </c>
       <c r="B16" t="n">
-        <v>78192</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445681</v>
+        <v>445726</v>
       </c>
       <c r="R16" t="n">
-        <v>7026315</v>
+        <v>7026295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130302606</v>
+        <v>130302583</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>83158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445694</v>
+        <v>445687</v>
       </c>
       <c r="R17" t="n">
-        <v>7026212</v>
+        <v>7026235</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,7 +2517,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130301089</v>
+        <v>130302606</v>
       </c>
       <c r="B18" t="n">
         <v>79180</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445726</v>
+        <v>445694</v>
       </c>
       <c r="R18" t="n">
-        <v>7026295</v>
+        <v>7026212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130302583</v>
+        <v>130302398</v>
       </c>
       <c r="B19" t="n">
-        <v>83158</v>
+        <v>78192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445687</v>
+        <v>445681</v>
       </c>
       <c r="R19" t="n">
-        <v>7026235</v>
+        <v>7026315</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3561,10 +3561,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130301166</v>
+        <v>130302477</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,46 +3572,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445711</v>
+        <v>445700</v>
       </c>
       <c r="R27" t="n">
-        <v>7026280</v>
+        <v>7026308</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,12 +3641,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3670,19 +3661,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130300326</v>
+        <v>130301166</v>
       </c>
       <c r="B28" t="n">
         <v>79180</v>
@@ -3712,7 +3703,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3726,13 +3717,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445796</v>
+        <v>445711</v>
       </c>
       <c r="R28" t="n">
-        <v>7026382</v>
+        <v>7026280</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3761,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,12 +3762,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3796,17 +3787,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130302477</v>
+        <v>130300326</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,37 +3805,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445700</v>
+        <v>445796</v>
       </c>
       <c r="R29" t="n">
-        <v>7026308</v>
+        <v>7026382</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,12 +3903,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130301748</v>
+        <v>130303378</v>
       </c>
       <c r="B3" t="n">
-        <v>80314</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445681</v>
+        <v>445813</v>
       </c>
       <c r="R3" t="n">
-        <v>7026210</v>
+        <v>7026366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +901,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130303378</v>
+        <v>130301748</v>
       </c>
       <c r="B4" t="n">
-        <v>91728</v>
+        <v>80314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445813</v>
+        <v>445681</v>
       </c>
       <c r="R4" t="n">
-        <v>7026366</v>
+        <v>7026210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130301915</v>
+        <v>130301787</v>
       </c>
       <c r="B36" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4602,37 +4602,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445762</v>
+        <v>445675</v>
       </c>
       <c r="R36" t="n">
-        <v>7026257</v>
+        <v>7026220</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4661,7 +4670,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4671,12 +4680,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4691,12 +4700,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4824,10 +4833,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301787</v>
+        <v>130301915</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,46 +4844,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445675</v>
+        <v>445762</v>
       </c>
       <c r="R38" t="n">
-        <v>7026220</v>
+        <v>7026257</v>
       </c>
       <c r="S38" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,12 +4933,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130303417</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130303378</v>
+        <v>130301748</v>
       </c>
       <c r="B3" t="n">
-        <v>91728</v>
+        <v>80317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445813</v>
+        <v>445681</v>
       </c>
       <c r="R3" t="n">
-        <v>7026366</v>
+        <v>7026210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +901,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130301748</v>
+        <v>130303378</v>
       </c>
       <c r="B4" t="n">
-        <v>80314</v>
+        <v>91731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445681</v>
+        <v>445813</v>
       </c>
       <c r="R4" t="n">
-        <v>7026210</v>
+        <v>7026366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
         <v>130301741</v>
       </c>
       <c r="B5" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>130303406</v>
       </c>
       <c r="B6" t="n">
-        <v>78192</v>
+        <v>78195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,62 +1244,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130303691</v>
+        <v>130301523</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>80316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445781</v>
+        <v>445674</v>
       </c>
       <c r="R7" t="n">
-        <v>7026394</v>
+        <v>7026247</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,12 +1324,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,7 +1349,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1373,7 +1359,7 @@
         <v>130300210</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,48 +1468,62 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130301523</v>
+        <v>130303691</v>
       </c>
       <c r="B9" t="n">
-        <v>80313</v>
+        <v>98923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445674</v>
+        <v>445781</v>
       </c>
       <c r="R9" t="n">
-        <v>7026247</v>
+        <v>7026394</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
         <v>130300764</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,32 +1715,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130303129</v>
+        <v>130302348</v>
       </c>
       <c r="B11" t="n">
-        <v>78192</v>
+        <v>91695</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445734</v>
+        <v>445688</v>
       </c>
       <c r="R11" t="n">
-        <v>7026229</v>
+        <v>7026324</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal gransumpskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,44 +1815,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130302348</v>
+        <v>130303129</v>
       </c>
       <c r="B12" t="n">
-        <v>91692</v>
+        <v>78195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445688</v>
+        <v>445734</v>
       </c>
       <c r="R12" t="n">
-        <v>7026324</v>
+        <v>7026229</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark på stam av levande gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
         <v>130300940</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>130301447</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130301555</v>
       </c>
       <c r="B15" t="n">
-        <v>97837</v>
+        <v>97840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130301089</v>
+        <v>130302583</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>83161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445726</v>
+        <v>445687</v>
       </c>
       <c r="R16" t="n">
-        <v>7026295</v>
+        <v>7026235</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130302583</v>
+        <v>130301089</v>
       </c>
       <c r="B17" t="n">
-        <v>83158</v>
+        <v>79183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445687</v>
+        <v>445726</v>
       </c>
       <c r="R17" t="n">
-        <v>7026235</v>
+        <v>7026295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,7 +2520,7 @@
         <v>130302606</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>130302398</v>
       </c>
       <c r="B19" t="n">
-        <v>78192</v>
+        <v>78195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2741,45 +2741,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130300536</v>
+        <v>130303722</v>
       </c>
       <c r="B20" t="n">
-        <v>97791</v>
+        <v>98923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445736</v>
+        <v>445791</v>
       </c>
       <c r="R20" t="n">
-        <v>7026373</v>
+        <v>7026379</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,12 +2835,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2846,66 +2860,52 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130303722</v>
+        <v>130300536</v>
       </c>
       <c r="B21" t="n">
-        <v>98920</v>
+        <v>97794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445791</v>
+        <v>445736</v>
       </c>
       <c r="R21" t="n">
-        <v>7026379</v>
+        <v>7026373</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
         <v>130303237</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>130301029</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130302646</v>
       </c>
       <c r="B24" t="n">
-        <v>97837</v>
+        <v>97840</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>130300161</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>130300508</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>130302477</v>
       </c>
       <c r="B27" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3673,42 +3673,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130301166</v>
+        <v>130303489</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>98923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3717,13 +3722,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445711</v>
+        <v>445824</v>
       </c>
       <c r="R28" t="n">
-        <v>7026280</v>
+        <v>7026381</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,7 +3757,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,12 +3767,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,17 +3792,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300326</v>
+        <v>130301166</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3829,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3838,13 +3843,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445796</v>
+        <v>445711</v>
       </c>
       <c r="R29" t="n">
-        <v>7026382</v>
+        <v>7026280</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3888,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3908,54 +3913,49 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130303489</v>
+        <v>130300326</v>
       </c>
       <c r="B30" t="n">
-        <v>98920</v>
+        <v>79183</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445824</v>
+        <v>445796</v>
       </c>
       <c r="R30" t="n">
-        <v>7026381</v>
+        <v>7026382</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
         <v>130301943</v>
       </c>
       <c r="B31" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>130301011</v>
       </c>
       <c r="B32" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4250,32 +4250,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130302719</v>
+        <v>130300852</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>75161</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445708</v>
+        <v>445737</v>
       </c>
       <c r="R33" t="n">
-        <v>7026207</v>
+        <v>7026346</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4362,48 +4362,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130300852</v>
+        <v>130302241</v>
       </c>
       <c r="B34" t="n">
-        <v>75158</v>
+        <v>91731</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445737</v>
+        <v>445762</v>
       </c>
       <c r="R34" t="n">
-        <v>7026346</v>
+        <v>7026257</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4432,7 +4437,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4442,12 +4447,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4462,22 +4467,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130302241</v>
+        <v>130302719</v>
       </c>
       <c r="B35" t="n">
-        <v>91728</v>
+        <v>79183</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4485,42 +4490,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445762</v>
+        <v>445708</v>
       </c>
       <c r="R35" t="n">
-        <v>7026257</v>
+        <v>7026207</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,12 +4579,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4594,7 +4594,7 @@
         <v>130301787</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130302963</v>
+        <v>130301915</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,46 +4723,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445703</v>
+        <v>445762</v>
       </c>
       <c r="R37" t="n">
-        <v>7026235</v>
+        <v>7026257</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4791,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4801,12 +4792,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,22 +4812,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301915</v>
+        <v>130302963</v>
       </c>
       <c r="B38" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,37 +4835,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445762</v>
+        <v>445703</v>
       </c>
       <c r="R38" t="n">
-        <v>7026257</v>
+        <v>7026235</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,12 +4933,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
         <v>130303099</v>
       </c>
       <c r="B39" t="n">
-        <v>78203</v>
+        <v>78206</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>130301433</v>
       </c>
       <c r="B40" t="n">
-        <v>79651</v>
+        <v>79654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>130301690</v>
       </c>
       <c r="B41" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130303417</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>130301748</v>
       </c>
       <c r="B3" t="n">
-        <v>80317</v>
+        <v>80343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>130303378</v>
       </c>
       <c r="B4" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>130301741</v>
       </c>
       <c r="B5" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>130303406</v>
       </c>
       <c r="B6" t="n">
-        <v>78195</v>
+        <v>78221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130301523</v>
+        <v>130300210</v>
       </c>
       <c r="B7" t="n">
-        <v>80316</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445674</v>
+        <v>445816</v>
       </c>
       <c r="R7" t="n">
-        <v>7026247</v>
+        <v>7026366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,39 +1349,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300210</v>
+        <v>130301523</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>80342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445816</v>
+        <v>445674</v>
       </c>
       <c r="R8" t="n">
-        <v>7026366</v>
+        <v>7026247</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
         <v>130303691</v>
       </c>
       <c r="B9" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>130300764</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130302348</v>
       </c>
       <c r="B11" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>130303129</v>
       </c>
       <c r="B12" t="n">
-        <v>78195</v>
+        <v>78221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>130300940</v>
       </c>
       <c r="B13" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,54 +2060,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130301447</v>
+        <v>130301555</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>97866</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445671</v>
+        <v>445699</v>
       </c>
       <c r="R14" t="n">
-        <v>7026257</v>
+        <v>7026231</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,12 +2140,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 200 år) i gammal granskog</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,52 +2165,61 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130301555</v>
+        <v>130301447</v>
       </c>
       <c r="B15" t="n">
-        <v>97840</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445699</v>
+        <v>445671</v>
       </c>
       <c r="R15" t="n">
-        <v>7026231</v>
+        <v>7026257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På gammal gran (ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,17 +2286,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130302583</v>
+        <v>130302398</v>
       </c>
       <c r="B16" t="n">
-        <v>83161</v>
+        <v>78221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445687</v>
+        <v>445681</v>
       </c>
       <c r="R16" t="n">
-        <v>7026235</v>
+        <v>7026315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,7 +2408,7 @@
         <v>130301089</v>
       </c>
       <c r="B17" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>130302606</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130302398</v>
+        <v>130302583</v>
       </c>
       <c r="B19" t="n">
-        <v>78195</v>
+        <v>83187</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445681</v>
+        <v>445687</v>
       </c>
       <c r="R19" t="n">
-        <v>7026315</v>
+        <v>7026235</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,7 +2744,7 @@
         <v>130303722</v>
       </c>
       <c r="B20" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>130300536</v>
       </c>
       <c r="B21" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>130303237</v>
       </c>
       <c r="B22" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>130301029</v>
       </c>
       <c r="B23" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130302646</v>
       </c>
       <c r="B24" t="n">
-        <v>97840</v>
+        <v>97866</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>130300161</v>
       </c>
       <c r="B25" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>130300508</v>
       </c>
       <c r="B26" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130302477</v>
+        <v>130301166</v>
       </c>
       <c r="B27" t="n">
-        <v>91731</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,37 +3572,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445700</v>
+        <v>445711</v>
       </c>
       <c r="R27" t="n">
-        <v>7026308</v>
+        <v>7026280</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3631,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,12 +3650,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,59 +3670,54 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130303489</v>
+        <v>130300326</v>
       </c>
       <c r="B28" t="n">
-        <v>98923</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3722,13 +3726,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445824</v>
+        <v>445796</v>
       </c>
       <c r="R28" t="n">
-        <v>7026381</v>
+        <v>7026382</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3757,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3767,12 +3771,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3792,17 +3796,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130301166</v>
+        <v>130302477</v>
       </c>
       <c r="B29" t="n">
-        <v>79183</v>
+        <v>91757</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3810,46 +3814,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445711</v>
+        <v>445700</v>
       </c>
       <c r="R29" t="n">
-        <v>7026280</v>
+        <v>7026308</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,12 +3883,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3908,54 +3903,59 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130300326</v>
+        <v>130303489</v>
       </c>
       <c r="B30" t="n">
-        <v>79183</v>
+        <v>98949</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445796</v>
+        <v>445824</v>
       </c>
       <c r="R30" t="n">
-        <v>7026382</v>
+        <v>7026381</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
         <v>130301943</v>
       </c>
       <c r="B31" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>130301011</v>
       </c>
       <c r="B32" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4250,32 +4250,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130300852</v>
+        <v>130302719</v>
       </c>
       <c r="B33" t="n">
-        <v>75161</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445737</v>
+        <v>445708</v>
       </c>
       <c r="R33" t="n">
-        <v>7026346</v>
+        <v>7026207</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4362,53 +4362,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130302241</v>
+        <v>130300852</v>
       </c>
       <c r="B34" t="n">
-        <v>91731</v>
+        <v>75187</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445762</v>
+        <v>445737</v>
       </c>
       <c r="R34" t="n">
-        <v>7026257</v>
+        <v>7026346</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4437,7 +4432,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4447,12 +4442,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4467,22 +4462,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130302719</v>
+        <v>130302241</v>
       </c>
       <c r="B35" t="n">
-        <v>79183</v>
+        <v>91757</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4490,37 +4485,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445708</v>
+        <v>445762</v>
       </c>
       <c r="R35" t="n">
-        <v>7026207</v>
+        <v>7026257</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,22 +4579,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130301787</v>
+        <v>130302963</v>
       </c>
       <c r="B36" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445675</v>
+        <v>445703</v>
       </c>
       <c r="R36" t="n">
-        <v>7026220</v>
+        <v>7026235</v>
       </c>
       <c r="S36" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4712,10 +4712,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130301915</v>
+        <v>130301787</v>
       </c>
       <c r="B37" t="n">
-        <v>80288</v>
+        <v>79209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,37 +4723,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445762</v>
+        <v>445675</v>
       </c>
       <c r="R37" t="n">
-        <v>7026257</v>
+        <v>7026220</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4782,7 +4791,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4792,12 +4801,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4812,22 +4821,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130302963</v>
+        <v>130301915</v>
       </c>
       <c r="B38" t="n">
-        <v>79183</v>
+        <v>80314</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,46 +4844,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445703</v>
+        <v>445762</v>
       </c>
       <c r="R38" t="n">
-        <v>7026235</v>
+        <v>7026257</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,12 +4933,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
         <v>130303099</v>
       </c>
       <c r="B39" t="n">
-        <v>78206</v>
+        <v>78232</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>130301433</v>
       </c>
       <c r="B40" t="n">
-        <v>79654</v>
+        <v>79680</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>130301690</v>
       </c>
       <c r="B41" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130300210</v>
+        <v>130301523</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>80342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445816</v>
+        <v>445674</v>
       </c>
       <c r="R7" t="n">
-        <v>7026366</v>
+        <v>7026247</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,39 +1349,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130301523</v>
+        <v>130300210</v>
       </c>
       <c r="B8" t="n">
-        <v>80342</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445674</v>
+        <v>445816</v>
       </c>
       <c r="R8" t="n">
-        <v>7026247</v>
+        <v>7026366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2060,45 +2060,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130301555</v>
+        <v>130301447</v>
       </c>
       <c r="B14" t="n">
-        <v>97866</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445699</v>
+        <v>445671</v>
       </c>
       <c r="R14" t="n">
-        <v>7026231</v>
+        <v>7026257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,12 +2149,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På gammal gran (ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,61 +2174,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130301447</v>
+        <v>130301555</v>
       </c>
       <c r="B15" t="n">
-        <v>79209</v>
+        <v>97866</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445671</v>
+        <v>445699</v>
       </c>
       <c r="R15" t="n">
-        <v>7026257</v>
+        <v>7026231</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 200 år) i gammal granskog</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130302963</v>
+        <v>130301915</v>
       </c>
       <c r="B36" t="n">
-        <v>79209</v>
+        <v>80314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4602,46 +4602,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445703</v>
+        <v>445762</v>
       </c>
       <c r="R36" t="n">
-        <v>7026235</v>
+        <v>7026257</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4670,7 +4661,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4680,12 +4671,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4700,19 +4691,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130301787</v>
+        <v>130302963</v>
       </c>
       <c r="B37" t="n">
         <v>79209</v>
@@ -4742,7 +4733,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4756,13 +4747,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445675</v>
+        <v>445703</v>
       </c>
       <c r="R37" t="n">
-        <v>7026220</v>
+        <v>7026235</v>
       </c>
       <c r="S37" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4791,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4801,12 +4792,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4833,10 +4824,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301915</v>
+        <v>130301787</v>
       </c>
       <c r="B38" t="n">
-        <v>80314</v>
+        <v>79209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,37 +4835,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445762</v>
+        <v>445675</v>
       </c>
       <c r="R38" t="n">
-        <v>7026257</v>
+        <v>7026220</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,12 +4933,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130301748</v>
+        <v>130303378</v>
       </c>
       <c r="B3" t="n">
-        <v>80343</v>
+        <v>91758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445681</v>
+        <v>445813</v>
       </c>
       <c r="R3" t="n">
-        <v>7026210</v>
+        <v>7026366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +901,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130303378</v>
+        <v>130301748</v>
       </c>
       <c r="B4" t="n">
-        <v>91757</v>
+        <v>80343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445813</v>
+        <v>445681</v>
       </c>
       <c r="R4" t="n">
-        <v>7026366</v>
+        <v>7026210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
         <v>130301741</v>
       </c>
       <c r="B5" t="n">
-        <v>83187</v>
+        <v>83188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130301523</v>
+        <v>130300210</v>
       </c>
       <c r="B7" t="n">
-        <v>80342</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445674</v>
+        <v>445816</v>
       </c>
       <c r="R7" t="n">
-        <v>7026247</v>
+        <v>7026366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,39 +1349,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300210</v>
+        <v>130301523</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>80342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445816</v>
+        <v>445674</v>
       </c>
       <c r="R8" t="n">
-        <v>7026366</v>
+        <v>7026247</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
         <v>130303691</v>
       </c>
       <c r="B9" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130302348</v>
       </c>
       <c r="B11" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130301555</v>
       </c>
       <c r="B15" t="n">
-        <v>97866</v>
+        <v>97867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130302398</v>
+        <v>130301089</v>
       </c>
       <c r="B16" t="n">
-        <v>78221</v>
+        <v>79209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445681</v>
+        <v>445726</v>
       </c>
       <c r="R16" t="n">
-        <v>7026315</v>
+        <v>7026295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,7 +2405,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130301089</v>
+        <v>130302606</v>
       </c>
       <c r="B17" t="n">
         <v>79209</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445726</v>
+        <v>445694</v>
       </c>
       <c r="R17" t="n">
-        <v>7026295</v>
+        <v>7026212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130302606</v>
+        <v>130302583</v>
       </c>
       <c r="B18" t="n">
-        <v>79209</v>
+        <v>83188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445694</v>
+        <v>445687</v>
       </c>
       <c r="R18" t="n">
-        <v>7026212</v>
+        <v>7026235</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130302583</v>
+        <v>130302398</v>
       </c>
       <c r="B19" t="n">
-        <v>83187</v>
+        <v>78221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445687</v>
+        <v>445681</v>
       </c>
       <c r="R19" t="n">
-        <v>7026235</v>
+        <v>7026315</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,7 +2744,7 @@
         <v>130303722</v>
       </c>
       <c r="B20" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>130300536</v>
       </c>
       <c r="B21" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130302646</v>
       </c>
       <c r="B24" t="n">
-        <v>97866</v>
+        <v>97867</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3561,42 +3561,47 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130301166</v>
+        <v>130303489</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>98950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3605,13 +3610,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445711</v>
+        <v>445824</v>
       </c>
       <c r="R27" t="n">
-        <v>7026280</v>
+        <v>7026381</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,12 +3655,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3675,17 +3680,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130300326</v>
+        <v>130302477</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>91758</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,46 +3698,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445796</v>
+        <v>445700</v>
       </c>
       <c r="R28" t="n">
-        <v>7026382</v>
+        <v>7026308</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,12 +3767,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3791,22 +3787,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130302477</v>
+        <v>130301166</v>
       </c>
       <c r="B29" t="n">
-        <v>91757</v>
+        <v>79209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,37 +3810,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445700</v>
+        <v>445711</v>
       </c>
       <c r="R29" t="n">
-        <v>7026308</v>
+        <v>7026280</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3888,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,59 +3908,54 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130303489</v>
+        <v>130300326</v>
       </c>
       <c r="B30" t="n">
-        <v>98949</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445824</v>
+        <v>445796</v>
       </c>
       <c r="R30" t="n">
-        <v>7026381</v>
+        <v>7026382</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130302719</v>
+        <v>130302241</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>91758</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,37 +4261,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445708</v>
+        <v>445762</v>
       </c>
       <c r="R33" t="n">
-        <v>7026207</v>
+        <v>7026257</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4330,12 +4335,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4350,44 +4355,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130300852</v>
+        <v>130302719</v>
       </c>
       <c r="B34" t="n">
-        <v>75187</v>
+        <v>79209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445737</v>
+        <v>445708</v>
       </c>
       <c r="R34" t="n">
-        <v>7026346</v>
+        <v>7026207</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4432,7 +4437,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4442,12 +4447,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4474,53 +4479,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130302241</v>
+        <v>130300852</v>
       </c>
       <c r="B35" t="n">
-        <v>91757</v>
+        <v>75187</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445762</v>
+        <v>445737</v>
       </c>
       <c r="R35" t="n">
-        <v>7026257</v>
+        <v>7026346</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,12 +4579,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>130303378</v>
       </c>
       <c r="B3" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>130301741</v>
       </c>
       <c r="B5" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130300210</v>
+        <v>130301523</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>80342</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445816</v>
+        <v>445674</v>
       </c>
       <c r="R7" t="n">
-        <v>7026366</v>
+        <v>7026247</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,55 +1349,69 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130301523</v>
+        <v>130303691</v>
       </c>
       <c r="B8" t="n">
-        <v>80342</v>
+        <v>98951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445674</v>
+        <v>445781</v>
       </c>
       <c r="R8" t="n">
-        <v>7026247</v>
+        <v>7026394</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,12 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,69 +1475,55 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130303691</v>
+        <v>130300210</v>
       </c>
       <c r="B9" t="n">
-        <v>98950</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445781</v>
+        <v>445816</v>
       </c>
       <c r="R9" t="n">
-        <v>7026394</v>
+        <v>7026366</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
         <v>130302348</v>
       </c>
       <c r="B11" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130301555</v>
       </c>
       <c r="B15" t="n">
-        <v>97867</v>
+        <v>97868</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130301089</v>
+        <v>130302398</v>
       </c>
       <c r="B16" t="n">
-        <v>79209</v>
+        <v>78221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445726</v>
+        <v>445681</v>
       </c>
       <c r="R16" t="n">
-        <v>7026295</v>
+        <v>7026315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,7 +2405,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130302606</v>
+        <v>130301089</v>
       </c>
       <c r="B17" t="n">
         <v>79209</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445694</v>
+        <v>445726</v>
       </c>
       <c r="R17" t="n">
-        <v>7026212</v>
+        <v>7026295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,7 +2520,7 @@
         <v>130302583</v>
       </c>
       <c r="B18" t="n">
-        <v>83188</v>
+        <v>83189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130302398</v>
+        <v>130302606</v>
       </c>
       <c r="B19" t="n">
-        <v>78221</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445681</v>
+        <v>445694</v>
       </c>
       <c r="R19" t="n">
-        <v>7026315</v>
+        <v>7026212</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,59 +2741,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130303722</v>
+        <v>130300536</v>
       </c>
       <c r="B20" t="n">
-        <v>98950</v>
+        <v>97822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445791</v>
+        <v>445736</v>
       </c>
       <c r="R20" t="n">
-        <v>7026379</v>
+        <v>7026373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,7 +2811,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,12 +2821,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,52 +2846,66 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130300536</v>
+        <v>130303722</v>
       </c>
       <c r="B21" t="n">
-        <v>97821</v>
+        <v>98951</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445736</v>
+        <v>445791</v>
       </c>
       <c r="R21" t="n">
-        <v>7026373</v>
+        <v>7026379</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3224,7 +3224,7 @@
         <v>130302646</v>
       </c>
       <c r="B24" t="n">
-        <v>97867</v>
+        <v>97868</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3561,62 +3561,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130303489</v>
+        <v>130302477</v>
       </c>
       <c r="B27" t="n">
-        <v>98950</v>
+        <v>91759</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445824</v>
+        <v>445700</v>
       </c>
       <c r="R27" t="n">
-        <v>7026381</v>
+        <v>7026308</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,12 +3641,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3675,22 +3661,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130302477</v>
+        <v>130301166</v>
       </c>
       <c r="B28" t="n">
-        <v>91758</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3698,37 +3684,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445700</v>
+        <v>445711</v>
       </c>
       <c r="R28" t="n">
-        <v>7026308</v>
+        <v>7026280</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3757,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3767,12 +3762,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,19 +3782,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130301166</v>
+        <v>130300326</v>
       </c>
       <c r="B29" t="n">
         <v>79209</v>
@@ -3829,7 +3824,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3843,13 +3838,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445711</v>
+        <v>445796</v>
       </c>
       <c r="R29" t="n">
-        <v>7026280</v>
+        <v>7026382</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,12 +3883,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3913,49 +3908,54 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130300326</v>
+        <v>130303489</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>98951</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445796</v>
+        <v>445824</v>
       </c>
       <c r="R30" t="n">
-        <v>7026382</v>
+        <v>7026381</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4250,53 +4250,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130302241</v>
+        <v>130300852</v>
       </c>
       <c r="B33" t="n">
-        <v>91758</v>
+        <v>75187</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445762</v>
+        <v>445737</v>
       </c>
       <c r="R33" t="n">
-        <v>7026257</v>
+        <v>7026346</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4335,12 +4330,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,12 +4350,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4479,48 +4474,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300852</v>
+        <v>130302241</v>
       </c>
       <c r="B35" t="n">
-        <v>75187</v>
+        <v>91759</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445737</v>
+        <v>445762</v>
       </c>
       <c r="R35" t="n">
-        <v>7026346</v>
+        <v>7026257</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,12 +4579,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130303417</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>130303378</v>
       </c>
       <c r="B3" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>130301748</v>
       </c>
       <c r="B4" t="n">
-        <v>80343</v>
+        <v>80345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>130301741</v>
       </c>
       <c r="B5" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>130303406</v>
       </c>
       <c r="B6" t="n">
-        <v>78221</v>
+        <v>78223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>130301523</v>
       </c>
       <c r="B7" t="n">
-        <v>80342</v>
+        <v>80344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,62 +1356,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130303691</v>
+        <v>130300210</v>
       </c>
       <c r="B8" t="n">
-        <v>98951</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445781</v>
+        <v>445816</v>
       </c>
       <c r="R8" t="n">
-        <v>7026394</v>
+        <v>7026366</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,12 +1436,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,55 +1461,69 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130300210</v>
+        <v>130303691</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>98953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445816</v>
+        <v>445781</v>
       </c>
       <c r="R9" t="n">
-        <v>7026366</v>
+        <v>7026394</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
         <v>130300764</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130302348</v>
       </c>
       <c r="B11" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>130303129</v>
       </c>
       <c r="B12" t="n">
-        <v>78221</v>
+        <v>78223</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>130300940</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>130301447</v>
       </c>
       <c r="B14" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130301555</v>
       </c>
       <c r="B15" t="n">
-        <v>97868</v>
+        <v>97870</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130302398</v>
+        <v>130301089</v>
       </c>
       <c r="B16" t="n">
-        <v>78221</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445681</v>
+        <v>445726</v>
       </c>
       <c r="R16" t="n">
-        <v>7026315</v>
+        <v>7026295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130301089</v>
+        <v>130302606</v>
       </c>
       <c r="B17" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445726</v>
+        <v>445694</v>
       </c>
       <c r="R17" t="n">
-        <v>7026295</v>
+        <v>7026212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,7 +2520,7 @@
         <v>130302583</v>
       </c>
       <c r="B18" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130302606</v>
+        <v>130302398</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>78223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445694</v>
+        <v>445681</v>
       </c>
       <c r="R19" t="n">
-        <v>7026212</v>
+        <v>7026315</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,45 +2741,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130300536</v>
+        <v>130303722</v>
       </c>
       <c r="B20" t="n">
-        <v>97822</v>
+        <v>98953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445736</v>
+        <v>445791</v>
       </c>
       <c r="R20" t="n">
-        <v>7026373</v>
+        <v>7026379</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,12 +2835,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2846,66 +2860,52 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130303722</v>
+        <v>130300536</v>
       </c>
       <c r="B21" t="n">
-        <v>98951</v>
+        <v>97824</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445791</v>
+        <v>445736</v>
       </c>
       <c r="R21" t="n">
-        <v>7026379</v>
+        <v>7026373</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
         <v>130303237</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>130301029</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130302646</v>
       </c>
       <c r="B24" t="n">
-        <v>97868</v>
+        <v>97870</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>130300161</v>
       </c>
       <c r="B25" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>130300508</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130302477</v>
+        <v>130301166</v>
       </c>
       <c r="B27" t="n">
-        <v>91759</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,37 +3572,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445700</v>
+        <v>445711</v>
       </c>
       <c r="R27" t="n">
-        <v>7026308</v>
+        <v>7026280</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3631,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,12 +3650,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,22 +3670,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130301166</v>
+        <v>130300326</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3712,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3717,13 +3726,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445711</v>
+        <v>445796</v>
       </c>
       <c r="R28" t="n">
-        <v>7026280</v>
+        <v>7026382</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,12 +3771,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,17 +3796,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300326</v>
+        <v>130302477</v>
       </c>
       <c r="B29" t="n">
-        <v>79209</v>
+        <v>91761</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,46 +3814,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445796</v>
+        <v>445700</v>
       </c>
       <c r="R29" t="n">
-        <v>7026382</v>
+        <v>7026308</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,12 +3903,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3918,7 +3918,7 @@
         <v>130303489</v>
       </c>
       <c r="B30" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130301943</v>
       </c>
       <c r="B31" t="n">
-        <v>80315</v>
+        <v>80317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
         <v>130301011</v>
       </c>
       <c r="B32" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4250,48 +4250,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130300852</v>
+        <v>130302241</v>
       </c>
       <c r="B33" t="n">
-        <v>75187</v>
+        <v>91761</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445737</v>
+        <v>445762</v>
       </c>
       <c r="R33" t="n">
-        <v>7026346</v>
+        <v>7026257</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4330,12 +4335,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4350,12 +4355,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4365,7 +4370,7 @@
         <v>130302719</v>
       </c>
       <c r="B34" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4474,53 +4479,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130302241</v>
+        <v>130300852</v>
       </c>
       <c r="B35" t="n">
-        <v>91759</v>
+        <v>75189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445762</v>
+        <v>445737</v>
       </c>
       <c r="R35" t="n">
-        <v>7026257</v>
+        <v>7026346</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,22 +4579,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130301915</v>
+        <v>130302963</v>
       </c>
       <c r="B36" t="n">
-        <v>80314</v>
+        <v>79211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4602,37 +4602,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445762</v>
+        <v>445703</v>
       </c>
       <c r="R36" t="n">
-        <v>7026257</v>
+        <v>7026235</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4661,7 +4670,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4671,12 +4680,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4691,22 +4700,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130302963</v>
+        <v>130301787</v>
       </c>
       <c r="B37" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,7 +4742,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4747,13 +4756,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445703</v>
+        <v>445675</v>
       </c>
       <c r="R37" t="n">
-        <v>7026235</v>
+        <v>7026220</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4782,7 +4791,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4792,12 +4801,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4824,10 +4833,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301787</v>
+        <v>130301915</v>
       </c>
       <c r="B38" t="n">
-        <v>79209</v>
+        <v>80316</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,46 +4844,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445675</v>
+        <v>445762</v>
       </c>
       <c r="R38" t="n">
-        <v>7026220</v>
+        <v>7026257</v>
       </c>
       <c r="S38" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,12 +4933,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
         <v>130303099</v>
       </c>
       <c r="B39" t="n">
-        <v>78232</v>
+        <v>78234</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>130301433</v>
       </c>
       <c r="B40" t="n">
-        <v>79680</v>
+        <v>79682</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>130301690</v>
       </c>
       <c r="B41" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130303378</v>
+        <v>130301748</v>
       </c>
       <c r="B3" t="n">
-        <v>91761</v>
+        <v>80345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445813</v>
+        <v>445681</v>
       </c>
       <c r="R3" t="n">
-        <v>7026366</v>
+        <v>7026210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +901,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130301748</v>
+        <v>130303378</v>
       </c>
       <c r="B4" t="n">
-        <v>80345</v>
+        <v>91761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445681</v>
+        <v>445813</v>
       </c>
       <c r="R4" t="n">
-        <v>7026210</v>
+        <v>7026366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130301523</v>
+        <v>130300210</v>
       </c>
       <c r="B7" t="n">
-        <v>80344</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445674</v>
+        <v>445816</v>
       </c>
       <c r="R7" t="n">
-        <v>7026247</v>
+        <v>7026366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,39 +1349,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300210</v>
+        <v>130301523</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>80344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445816</v>
+        <v>445674</v>
       </c>
       <c r="R8" t="n">
-        <v>7026366</v>
+        <v>7026247</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
         <v>130303691</v>
       </c>
       <c r="B9" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130301555</v>
       </c>
       <c r="B15" t="n">
-        <v>97870</v>
+        <v>97874</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130301089</v>
+        <v>130302398</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>78223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445726</v>
+        <v>445681</v>
       </c>
       <c r="R16" t="n">
-        <v>7026295</v>
+        <v>7026315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,7 +2405,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130302606</v>
+        <v>130301089</v>
       </c>
       <c r="B17" t="n">
         <v>79211</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445694</v>
+        <v>445726</v>
       </c>
       <c r="R17" t="n">
-        <v>7026212</v>
+        <v>7026295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130302583</v>
+        <v>130302606</v>
       </c>
       <c r="B18" t="n">
-        <v>83191</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445687</v>
+        <v>445694</v>
       </c>
       <c r="R18" t="n">
-        <v>7026235</v>
+        <v>7026212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130302398</v>
+        <v>130302583</v>
       </c>
       <c r="B19" t="n">
-        <v>78223</v>
+        <v>83191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445681</v>
+        <v>445687</v>
       </c>
       <c r="R19" t="n">
-        <v>7026315</v>
+        <v>7026235</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,7 +2744,7 @@
         <v>130303722</v>
       </c>
       <c r="B20" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>130300536</v>
       </c>
       <c r="B21" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130302646</v>
       </c>
       <c r="B24" t="n">
-        <v>97870</v>
+        <v>97874</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3561,10 +3561,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130301166</v>
+        <v>130302477</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,46 +3572,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445711</v>
+        <v>445700</v>
       </c>
       <c r="R27" t="n">
-        <v>7026280</v>
+        <v>7026308</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,12 +3641,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3670,12 +3661,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3803,48 +3794,62 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130302477</v>
+        <v>130303489</v>
       </c>
       <c r="B29" t="n">
-        <v>91761</v>
+        <v>98957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445700</v>
+        <v>445824</v>
       </c>
       <c r="R29" t="n">
-        <v>7026308</v>
+        <v>7026381</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3888,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,59 +3908,54 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130303489</v>
+        <v>130301166</v>
       </c>
       <c r="B30" t="n">
-        <v>98953</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445824</v>
+        <v>445711</v>
       </c>
       <c r="R30" t="n">
-        <v>7026381</v>
+        <v>7026280</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130301787</v>
+        <v>130301915</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,46 +4723,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445675</v>
+        <v>445762</v>
       </c>
       <c r="R37" t="n">
-        <v>7026220</v>
+        <v>7026257</v>
       </c>
       <c r="S37" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4791,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4801,12 +4792,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,22 +4812,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301915</v>
+        <v>130301787</v>
       </c>
       <c r="B38" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,37 +4835,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445762</v>
+        <v>445675</v>
       </c>
       <c r="R38" t="n">
-        <v>7026257</v>
+        <v>7026220</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,22 +4933,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130303099</v>
+        <v>130301433</v>
       </c>
       <c r="B39" t="n">
-        <v>78234</v>
+        <v>79682</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>314</v>
+        <v>1797</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4980,13 +4980,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445734</v>
+        <v>445678</v>
       </c>
       <c r="R39" t="n">
-        <v>7026229</v>
+        <v>7026239</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran (ca 200 år) i gammal gransumpskog</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5045,22 +5045,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130301433</v>
+        <v>130303099</v>
       </c>
       <c r="B40" t="n">
-        <v>79682</v>
+        <v>78234</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1797</v>
+        <v>314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5092,13 +5092,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445678</v>
+        <v>445734</v>
       </c>
       <c r="R40" t="n">
-        <v>7026239</v>
+        <v>7026229</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>På bark på undersidan av död gren på gammal levande gran (ca 200 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5157,12 +5157,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5294,6 +5294,1346 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130719426</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>445709</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7026371</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal levande gran (42 cm dbh, ca 170 år) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130719742</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>445734</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7026264</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal gran i gles gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130719785</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78223</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>445739</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7026240</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130719248</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>445790</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7026392</v>
+      </c>
+      <c r="S45" t="n">
+        <v>8</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130719929</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>445789</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7026327</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130719892</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>445759</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7026307</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1000 bålar fördelat på 10 gamla granar i gammal granskog, längsta bållängd 70 cm</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130719486</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91757</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>445689</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7026360</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På granhögstubbe i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130719818</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>445747</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7026270</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande gran (24 cm dbh, ca 200 år) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130719759</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>445728</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7026253</v>
+      </c>
+      <c r="S50" t="n">
+        <v>7</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>40 bålar på 200-årig tall i gles gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130719533</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91757</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>445674</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7026358</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På granhögstubbe (40 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130719350</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79211</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>445746</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7026368</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Draperat på 200-årig gammal levande gran i gammal granskog, längsta bål 60 cm</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130302398</v>
+        <v>130301089</v>
       </c>
       <c r="B16" t="n">
-        <v>78223</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445681</v>
+        <v>445726</v>
       </c>
       <c r="R16" t="n">
-        <v>7026315</v>
+        <v>7026295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130301089</v>
+        <v>130302398</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>78223</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445726</v>
+        <v>445681</v>
       </c>
       <c r="R17" t="n">
-        <v>7026295</v>
+        <v>7026315</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2741,59 +2741,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130303722</v>
+        <v>130300536</v>
       </c>
       <c r="B20" t="n">
-        <v>98957</v>
+        <v>97828</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445791</v>
+        <v>445736</v>
       </c>
       <c r="R20" t="n">
-        <v>7026379</v>
+        <v>7026373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,7 +2811,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,12 +2821,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,52 +2846,66 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130300536</v>
+        <v>130303722</v>
       </c>
       <c r="B21" t="n">
-        <v>97828</v>
+        <v>98957</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445736</v>
+        <v>445791</v>
       </c>
       <c r="R21" t="n">
-        <v>7026373</v>
+        <v>7026379</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3561,48 +3561,62 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130302477</v>
+        <v>130303489</v>
       </c>
       <c r="B27" t="n">
-        <v>91761</v>
+        <v>98957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445700</v>
+        <v>445824</v>
       </c>
       <c r="R27" t="n">
-        <v>7026308</v>
+        <v>7026381</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3631,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,12 +3655,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,7 +3675,7 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3673,7 +3687,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130300326</v>
+        <v>130301166</v>
       </c>
       <c r="B28" t="n">
         <v>79211</v>
@@ -3703,7 +3717,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3717,13 +3731,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445796</v>
+        <v>445711</v>
       </c>
       <c r="R28" t="n">
-        <v>7026382</v>
+        <v>7026280</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,7 +3766,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,12 +3776,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,54 +3801,49 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130303489</v>
+        <v>130300326</v>
       </c>
       <c r="B29" t="n">
-        <v>98957</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3843,13 +3852,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445824</v>
+        <v>445796</v>
       </c>
       <c r="R29" t="n">
-        <v>7026381</v>
+        <v>7026382</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,7 +3887,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,12 +3897,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3913,17 +3922,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130301166</v>
+        <v>130302477</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,46 +3940,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445711</v>
+        <v>445700</v>
       </c>
       <c r="R30" t="n">
-        <v>7026280</v>
+        <v>7026308</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,12 +4029,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130302963</v>
+        <v>130301915</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4602,46 +4602,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445703</v>
+        <v>445762</v>
       </c>
       <c r="R36" t="n">
-        <v>7026235</v>
+        <v>7026257</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4670,7 +4661,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4680,12 +4671,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4700,22 +4691,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130301915</v>
+        <v>130302963</v>
       </c>
       <c r="B37" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,37 +4714,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445762</v>
+        <v>445703</v>
       </c>
       <c r="R37" t="n">
-        <v>7026257</v>
+        <v>7026235</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4812,12 +4812,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130301433</v>
+        <v>130303099</v>
       </c>
       <c r="B39" t="n">
-        <v>79682</v>
+        <v>78234</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1797</v>
+        <v>314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4980,13 +4980,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445678</v>
+        <v>445734</v>
       </c>
       <c r="R39" t="n">
-        <v>7026239</v>
+        <v>7026229</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>På bark på undersidan av död gren på gammal levande gran (ca 200 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5045,22 +5045,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130303099</v>
+        <v>130301433</v>
       </c>
       <c r="B40" t="n">
-        <v>78234</v>
+        <v>79682</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>314</v>
+        <v>1797</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5092,13 +5092,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445734</v>
+        <v>445678</v>
       </c>
       <c r="R40" t="n">
-        <v>7026229</v>
+        <v>7026239</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran (ca 200 år) i gammal gransumpskog</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5157,12 +5157,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130719742</v>
+        <v>130719785</v>
       </c>
       <c r="B43" t="n">
-        <v>79211</v>
+        <v>78223</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,43 +5419,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445734</v>
+        <v>445739</v>
       </c>
       <c r="R43" t="n">
-        <v>7026264</v>
+        <v>7026240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5487,7 +5478,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,12 +5488,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5529,10 +5520,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130719785</v>
+        <v>130719742</v>
       </c>
       <c r="B44" t="n">
-        <v>78223</v>
+        <v>79211</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5540,34 +5531,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445739</v>
+        <v>445734</v>
       </c>
       <c r="R44" t="n">
-        <v>7026240</v>
+        <v>7026264</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130301748</v>
+        <v>130303378</v>
       </c>
       <c r="B3" t="n">
-        <v>80345</v>
+        <v>91761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445681</v>
+        <v>445813</v>
       </c>
       <c r="R3" t="n">
-        <v>7026210</v>
+        <v>7026366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +901,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130303378</v>
+        <v>130301748</v>
       </c>
       <c r="B4" t="n">
-        <v>91761</v>
+        <v>80345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445813</v>
+        <v>445681</v>
       </c>
       <c r="R4" t="n">
-        <v>7026366</v>
+        <v>7026210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130301089</v>
+        <v>130302398</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>78223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445726</v>
+        <v>445681</v>
       </c>
       <c r="R16" t="n">
-        <v>7026295</v>
+        <v>7026315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130302398</v>
+        <v>130302606</v>
       </c>
       <c r="B17" t="n">
-        <v>78223</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445681</v>
+        <v>445694</v>
       </c>
       <c r="R17" t="n">
-        <v>7026315</v>
+        <v>7026212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,7 +2517,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130302606</v>
+        <v>130301089</v>
       </c>
       <c r="B18" t="n">
         <v>79211</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445694</v>
+        <v>445726</v>
       </c>
       <c r="R18" t="n">
-        <v>7026212</v>
+        <v>7026295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2979,54 +2979,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130303237</v>
+        <v>130302646</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>97874</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445744</v>
+        <v>445702</v>
       </c>
       <c r="R22" t="n">
-        <v>7026231</v>
+        <v>7026205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3058,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3068,12 +3059,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3221,45 +3212,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130302646</v>
+        <v>130303237</v>
       </c>
       <c r="B24" t="n">
-        <v>97874</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445702</v>
+        <v>445744</v>
       </c>
       <c r="R24" t="n">
-        <v>7026205</v>
+        <v>7026231</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3561,47 +3561,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130303489</v>
+        <v>130300326</v>
       </c>
       <c r="B27" t="n">
-        <v>98957</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3610,13 +3605,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445824</v>
+        <v>445796</v>
       </c>
       <c r="R27" t="n">
-        <v>7026381</v>
+        <v>7026382</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,12 +3650,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3680,7 +3675,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3808,10 +3803,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300326</v>
+        <v>130302477</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,46 +3814,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445796</v>
+        <v>445700</v>
       </c>
       <c r="R29" t="n">
-        <v>7026382</v>
+        <v>7026308</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3887,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3897,12 +3883,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3917,60 +3903,74 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130302477</v>
+        <v>130303489</v>
       </c>
       <c r="B30" t="n">
-        <v>91761</v>
+        <v>98957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445700</v>
+        <v>445824</v>
       </c>
       <c r="R30" t="n">
-        <v>7026308</v>
+        <v>7026381</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,12 +4029,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4367,32 +4367,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130302719</v>
+        <v>130300852</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>75189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445708</v>
+        <v>445737</v>
       </c>
       <c r="R34" t="n">
-        <v>7026207</v>
+        <v>7026346</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4479,32 +4479,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300852</v>
+        <v>130302719</v>
       </c>
       <c r="B35" t="n">
-        <v>75189</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445737</v>
+        <v>445708</v>
       </c>
       <c r="R35" t="n">
-        <v>7026346</v>
+        <v>7026207</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4591,10 +4591,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130301915</v>
+        <v>130301787</v>
       </c>
       <c r="B36" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4602,37 +4602,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445762</v>
+        <v>445675</v>
       </c>
       <c r="R36" t="n">
-        <v>7026257</v>
+        <v>7026220</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4661,7 +4670,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4671,12 +4680,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4691,22 +4700,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130302963</v>
+        <v>130301915</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4714,46 +4723,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445703</v>
+        <v>445762</v>
       </c>
       <c r="R37" t="n">
-        <v>7026235</v>
+        <v>7026257</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4812,19 +4812,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301787</v>
+        <v>130302963</v>
       </c>
       <c r="B38" t="n">
         <v>79211</v>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4868,13 +4868,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445675</v>
+        <v>445703</v>
       </c>
       <c r="R38" t="n">
-        <v>7026220</v>
+        <v>7026235</v>
       </c>
       <c r="S38" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5408,10 +5408,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130719785</v>
+        <v>130719742</v>
       </c>
       <c r="B43" t="n">
-        <v>78223</v>
+        <v>79211</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,34 +5419,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445739</v>
+        <v>445734</v>
       </c>
       <c r="R43" t="n">
-        <v>7026240</v>
+        <v>7026264</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5478,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5488,12 +5497,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5520,7 +5529,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130719742</v>
+        <v>130719248</v>
       </c>
       <c r="B44" t="n">
         <v>79211</v>
@@ -5550,7 +5559,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5564,13 +5573,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445734</v>
+        <v>445790</v>
       </c>
       <c r="R44" t="n">
-        <v>7026264</v>
+        <v>7026392</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5599,7 +5608,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5609,12 +5618,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5625,6 +5634,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5641,10 +5665,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130719248</v>
+        <v>130719785</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>78223</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5652,46 +5676,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445790</v>
+        <v>445739</v>
       </c>
       <c r="R45" t="n">
-        <v>7026392</v>
+        <v>7026240</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5720,7 +5735,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5730,12 +5745,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5746,21 +5761,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130301741</v>
+        <v>130303406</v>
       </c>
       <c r="B5" t="n">
-        <v>83191</v>
+        <v>78223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445718</v>
+        <v>445827</v>
       </c>
       <c r="R5" t="n">
-        <v>7026281</v>
+        <v>7026371</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130303406</v>
+        <v>130301741</v>
       </c>
       <c r="B6" t="n">
-        <v>78223</v>
+        <v>83191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445827</v>
+        <v>445718</v>
       </c>
       <c r="R6" t="n">
-        <v>7026371</v>
+        <v>7026281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,60 +1232,74 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130300210</v>
+        <v>130303691</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>98957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445816</v>
+        <v>445781</v>
       </c>
       <c r="R7" t="n">
-        <v>7026366</v>
+        <v>7026394</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1338,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,39 +1363,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130301523</v>
+        <v>130300210</v>
       </c>
       <c r="B8" t="n">
-        <v>80344</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445674</v>
+        <v>445816</v>
       </c>
       <c r="R8" t="n">
-        <v>7026247</v>
+        <v>7026366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,12 +1450,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,69 +1475,55 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130303691</v>
+        <v>130301523</v>
       </c>
       <c r="B9" t="n">
-        <v>98957</v>
+        <v>80344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445781</v>
+        <v>445674</v>
       </c>
       <c r="R9" t="n">
-        <v>7026394</v>
+        <v>7026247</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1939,54 +1939,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130300940</v>
+        <v>130301555</v>
       </c>
       <c r="B13" t="n">
-        <v>79211</v>
+        <v>97874</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445746</v>
+        <v>445699</v>
       </c>
       <c r="R13" t="n">
-        <v>7026325</v>
+        <v>7026231</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,12 +2019,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,14 +2044,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130301447</v>
+        <v>130300940</v>
       </c>
       <c r="B14" t="n">
         <v>79211</v>
@@ -2104,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445671</v>
+        <v>445746</v>
       </c>
       <c r="R14" t="n">
-        <v>7026257</v>
+        <v>7026325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,12 +2140,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 200 år) i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,45 +2172,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130301555</v>
+        <v>130301447</v>
       </c>
       <c r="B15" t="n">
-        <v>97874</v>
+        <v>79211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445699</v>
+        <v>445671</v>
       </c>
       <c r="R15" t="n">
-        <v>7026231</v>
+        <v>7026257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På gammal gran (ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130302606</v>
+        <v>130301089</v>
       </c>
       <c r="B17" t="n">
         <v>79211</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445694</v>
+        <v>445726</v>
       </c>
       <c r="R17" t="n">
-        <v>7026212</v>
+        <v>7026295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,7 +2517,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130301089</v>
+        <v>130302606</v>
       </c>
       <c r="B18" t="n">
         <v>79211</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445726</v>
+        <v>445694</v>
       </c>
       <c r="R18" t="n">
-        <v>7026295</v>
+        <v>7026212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2979,45 +2979,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130302646</v>
+        <v>130303237</v>
       </c>
       <c r="B22" t="n">
-        <v>97874</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445702</v>
+        <v>445744</v>
       </c>
       <c r="R22" t="n">
-        <v>7026205</v>
+        <v>7026231</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3058,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,12 +3068,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3212,54 +3221,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130303237</v>
+        <v>130302646</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>97874</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445744</v>
+        <v>445702</v>
       </c>
       <c r="R24" t="n">
-        <v>7026231</v>
+        <v>7026205</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3561,42 +3561,47 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130300326</v>
+        <v>130303489</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>98957</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3605,13 +3610,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445796</v>
+        <v>445824</v>
       </c>
       <c r="R27" t="n">
-        <v>7026382</v>
+        <v>7026381</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,12 +3655,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3675,7 +3680,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3803,10 +3808,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130302477</v>
+        <v>130300326</v>
       </c>
       <c r="B29" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,37 +3819,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445700</v>
+        <v>445796</v>
       </c>
       <c r="R29" t="n">
-        <v>7026308</v>
+        <v>7026382</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3887,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3897,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,74 +3917,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130303489</v>
+        <v>130302477</v>
       </c>
       <c r="B30" t="n">
-        <v>98957</v>
+        <v>91761</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445824</v>
+        <v>445700</v>
       </c>
       <c r="R30" t="n">
-        <v>7026381</v>
+        <v>7026308</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,12 +4029,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130302241</v>
+        <v>130302719</v>
       </c>
       <c r="B33" t="n">
-        <v>91761</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,42 +4261,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445762</v>
+        <v>445708</v>
       </c>
       <c r="R33" t="n">
-        <v>7026257</v>
+        <v>7026207</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4335,12 +4330,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,12 +4350,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4479,10 +4474,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130302719</v>
+        <v>130302241</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>91761</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4490,37 +4485,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445708</v>
+        <v>445762</v>
       </c>
       <c r="R35" t="n">
-        <v>7026207</v>
+        <v>7026257</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,19 +4579,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130301787</v>
+        <v>130302963</v>
       </c>
       <c r="B36" t="n">
         <v>79211</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445675</v>
+        <v>445703</v>
       </c>
       <c r="R36" t="n">
-        <v>7026220</v>
+        <v>7026235</v>
       </c>
       <c r="S36" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4712,10 +4712,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130301915</v>
+        <v>130301787</v>
       </c>
       <c r="B37" t="n">
-        <v>80316</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,37 +4723,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445762</v>
+        <v>445675</v>
       </c>
       <c r="R37" t="n">
-        <v>7026257</v>
+        <v>7026220</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4782,7 +4791,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4792,12 +4801,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4812,22 +4821,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130302963</v>
+        <v>130301915</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>80316</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,46 +4844,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445703</v>
+        <v>445762</v>
       </c>
       <c r="R38" t="n">
-        <v>7026235</v>
+        <v>7026257</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,12 +4933,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130303417</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130303378</v>
+        <v>130301748</v>
       </c>
       <c r="B3" t="n">
-        <v>91761</v>
+        <v>80353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445813</v>
+        <v>445681</v>
       </c>
       <c r="R3" t="n">
-        <v>7026366</v>
+        <v>7026210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +901,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130301748</v>
+        <v>130303378</v>
       </c>
       <c r="B4" t="n">
-        <v>80345</v>
+        <v>91774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445681</v>
+        <v>445813</v>
       </c>
       <c r="R4" t="n">
-        <v>7026210</v>
+        <v>7026366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
         <v>130303406</v>
       </c>
       <c r="B5" t="n">
-        <v>78223</v>
+        <v>78231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>130301741</v>
       </c>
       <c r="B6" t="n">
-        <v>83191</v>
+        <v>83199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>130303691</v>
       </c>
       <c r="B7" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>130300210</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>130301523</v>
       </c>
       <c r="B9" t="n">
-        <v>80344</v>
+        <v>80352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>130300764</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130302348</v>
       </c>
       <c r="B11" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>130303129</v>
       </c>
       <c r="B12" t="n">
-        <v>78223</v>
+        <v>78231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,45 +1939,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130301555</v>
+        <v>130300940</v>
       </c>
       <c r="B13" t="n">
-        <v>97874</v>
+        <v>79219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445699</v>
+        <v>445746</v>
       </c>
       <c r="R13" t="n">
-        <v>7026231</v>
+        <v>7026325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,12 +2028,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,17 +2053,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130300940</v>
+        <v>130301447</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445746</v>
+        <v>445671</v>
       </c>
       <c r="R14" t="n">
-        <v>7026325</v>
+        <v>7026257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,12 +2149,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På gammal gran (ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,54 +2181,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130301447</v>
+        <v>130301555</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>97887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445671</v>
+        <v>445699</v>
       </c>
       <c r="R15" t="n">
-        <v>7026257</v>
+        <v>7026231</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 200 år) i gammal granskog</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,17 +2286,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130302398</v>
+        <v>130301089</v>
       </c>
       <c r="B16" t="n">
-        <v>78223</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445681</v>
+        <v>445726</v>
       </c>
       <c r="R16" t="n">
-        <v>7026315</v>
+        <v>7026295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130301089</v>
+        <v>130302606</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445726</v>
+        <v>445694</v>
       </c>
       <c r="R17" t="n">
-        <v>7026295</v>
+        <v>7026212</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130302606</v>
+        <v>130302583</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>83199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445694</v>
+        <v>445687</v>
       </c>
       <c r="R18" t="n">
-        <v>7026212</v>
+        <v>7026235</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130302583</v>
+        <v>130302398</v>
       </c>
       <c r="B19" t="n">
-        <v>83191</v>
+        <v>78231</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445687</v>
+        <v>445681</v>
       </c>
       <c r="R19" t="n">
-        <v>7026235</v>
+        <v>7026315</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,7 +2744,7 @@
         <v>130300536</v>
       </c>
       <c r="B20" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>130303722</v>
       </c>
       <c r="B21" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>130303237</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>130301029</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>130302646</v>
       </c>
       <c r="B24" t="n">
-        <v>97874</v>
+        <v>97887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>130300161</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>130300508</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3561,47 +3561,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130303489</v>
+        <v>130301166</v>
       </c>
       <c r="B27" t="n">
-        <v>98957</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3610,13 +3605,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445824</v>
+        <v>445711</v>
       </c>
       <c r="R27" t="n">
-        <v>7026381</v>
+        <v>7026280</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,12 +3650,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3680,17 +3675,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130301166</v>
+        <v>130300326</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,7 +3712,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3731,13 +3726,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445711</v>
+        <v>445796</v>
       </c>
       <c r="R28" t="n">
-        <v>7026280</v>
+        <v>7026382</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3766,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3776,12 +3771,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3801,17 +3796,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300326</v>
+        <v>130302477</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>91774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,46 +3814,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445796</v>
+        <v>445700</v>
       </c>
       <c r="R29" t="n">
-        <v>7026382</v>
+        <v>7026308</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3887,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3897,12 +3883,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3917,60 +3903,74 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130302477</v>
+        <v>130303489</v>
       </c>
       <c r="B30" t="n">
-        <v>91761</v>
+        <v>98970</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445700</v>
+        <v>445824</v>
       </c>
       <c r="R30" t="n">
-        <v>7026308</v>
+        <v>7026381</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,12 +4029,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
         <v>130301943</v>
       </c>
       <c r="B31" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4156,7 +4156,7 @@
         <v>130301011</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130302719</v>
+        <v>130302241</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>91774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,37 +4261,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445708</v>
+        <v>445762</v>
       </c>
       <c r="R33" t="n">
-        <v>7026207</v>
+        <v>7026257</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4330,12 +4335,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4350,44 +4355,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130300852</v>
+        <v>130302719</v>
       </c>
       <c r="B34" t="n">
-        <v>75189</v>
+        <v>79219</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445737</v>
+        <v>445708</v>
       </c>
       <c r="R34" t="n">
-        <v>7026346</v>
+        <v>7026207</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4432,7 +4437,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4442,12 +4447,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4474,53 +4479,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130302241</v>
+        <v>130300852</v>
       </c>
       <c r="B35" t="n">
-        <v>91761</v>
+        <v>75197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445762</v>
+        <v>445737</v>
       </c>
       <c r="R35" t="n">
-        <v>7026257</v>
+        <v>7026346</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,12 +4579,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4594,7 +4594,7 @@
         <v>130302963</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130301787</v>
+        <v>130301915</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>80324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,46 +4723,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445675</v>
+        <v>445762</v>
       </c>
       <c r="R37" t="n">
-        <v>7026220</v>
+        <v>7026257</v>
       </c>
       <c r="S37" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4791,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4801,12 +4792,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,22 +4812,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301915</v>
+        <v>130301787</v>
       </c>
       <c r="B38" t="n">
-        <v>80316</v>
+        <v>79219</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,37 +4835,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445762</v>
+        <v>445675</v>
       </c>
       <c r="R38" t="n">
-        <v>7026257</v>
+        <v>7026220</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,12 +4933,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
         <v>130303099</v>
       </c>
       <c r="B39" t="n">
-        <v>78234</v>
+        <v>78242</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>130301433</v>
       </c>
       <c r="B40" t="n">
-        <v>79682</v>
+        <v>79690</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>130301690</v>
       </c>
       <c r="B41" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>130719426</v>
       </c>
       <c r="B42" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130719742</v>
+        <v>130719785</v>
       </c>
       <c r="B43" t="n">
-        <v>79211</v>
+        <v>78231</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,43 +5419,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445734</v>
+        <v>445739</v>
       </c>
       <c r="R43" t="n">
-        <v>7026264</v>
+        <v>7026240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5487,7 +5478,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,12 +5488,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5529,10 +5520,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130719248</v>
+        <v>130719742</v>
       </c>
       <c r="B44" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5559,7 +5550,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5573,13 +5564,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445790</v>
+        <v>445734</v>
       </c>
       <c r="R44" t="n">
-        <v>7026392</v>
+        <v>7026264</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5608,7 +5599,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5618,12 +5609,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5634,21 +5625,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5665,10 +5641,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130719785</v>
+        <v>130719248</v>
       </c>
       <c r="B45" t="n">
-        <v>78223</v>
+        <v>79219</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5676,37 +5652,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445739</v>
+        <v>445790</v>
       </c>
       <c r="R45" t="n">
-        <v>7026240</v>
+        <v>7026392</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5735,7 +5720,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5745,12 +5730,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5761,6 +5746,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5780,7 +5780,7 @@
         <v>130719929</v>
       </c>
       <c r="B46" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>130719892</v>
       </c>
       <c r="B47" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>130719486</v>
       </c>
       <c r="B48" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130719818</v>
       </c>
       <c r="B49" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>130719759</v>
       </c>
       <c r="B50" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>130719533</v>
       </c>
       <c r="B51" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>130719350</v>
       </c>
       <c r="B52" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130303417</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130301748</v>
+        <v>130303378</v>
       </c>
       <c r="B3" t="n">
-        <v>80353</v>
+        <v>91775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445681</v>
+        <v>445813</v>
       </c>
       <c r="R3" t="n">
-        <v>7026210</v>
+        <v>7026366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +901,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130303378</v>
+        <v>130301748</v>
       </c>
       <c r="B4" t="n">
-        <v>91774</v>
+        <v>80354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445813</v>
+        <v>445681</v>
       </c>
       <c r="R4" t="n">
-        <v>7026366</v>
+        <v>7026210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
         <v>130303406</v>
       </c>
       <c r="B5" t="n">
-        <v>78231</v>
+        <v>78232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>130301741</v>
       </c>
       <c r="B6" t="n">
-        <v>83199</v>
+        <v>83200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,62 +1244,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130303691</v>
+        <v>130300210</v>
       </c>
       <c r="B7" t="n">
-        <v>98970</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445781</v>
+        <v>445816</v>
       </c>
       <c r="R7" t="n">
-        <v>7026394</v>
+        <v>7026366</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,12 +1324,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,39 +1349,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300210</v>
+        <v>130301523</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>80353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445816</v>
+        <v>445674</v>
       </c>
       <c r="R8" t="n">
-        <v>7026366</v>
+        <v>7026247</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,12 +1436,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,55 +1461,69 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130301523</v>
+        <v>130303691</v>
       </c>
       <c r="B9" t="n">
-        <v>80352</v>
+        <v>98971</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445674</v>
+        <v>445781</v>
       </c>
       <c r="R9" t="n">
-        <v>7026247</v>
+        <v>7026394</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
         <v>130300764</v>
       </c>
       <c r="B10" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130302348</v>
       </c>
       <c r="B11" t="n">
-        <v>91737</v>
+        <v>91738</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>130303129</v>
       </c>
       <c r="B12" t="n">
-        <v>78231</v>
+        <v>78232</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>130300940</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>130301447</v>
       </c>
       <c r="B14" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130301555</v>
       </c>
       <c r="B15" t="n">
-        <v>97887</v>
+        <v>97888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>130301089</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>130302606</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130302583</v>
+        <v>130302398</v>
       </c>
       <c r="B18" t="n">
-        <v>83199</v>
+        <v>78232</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445687</v>
+        <v>445681</v>
       </c>
       <c r="R18" t="n">
-        <v>7026235</v>
+        <v>7026315</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,10 +2629,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130302398</v>
+        <v>130302583</v>
       </c>
       <c r="B19" t="n">
-        <v>78231</v>
+        <v>83200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445681</v>
+        <v>445687</v>
       </c>
       <c r="R19" t="n">
-        <v>7026315</v>
+        <v>7026235</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,45 +2741,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130300536</v>
+        <v>130303722</v>
       </c>
       <c r="B20" t="n">
-        <v>97841</v>
+        <v>98971</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445736</v>
+        <v>445791</v>
       </c>
       <c r="R20" t="n">
-        <v>7026373</v>
+        <v>7026379</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,12 +2835,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2846,66 +2860,52 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130303722</v>
+        <v>130300536</v>
       </c>
       <c r="B21" t="n">
-        <v>98970</v>
+        <v>97842</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445791</v>
+        <v>445736</v>
       </c>
       <c r="R21" t="n">
-        <v>7026379</v>
+        <v>7026373</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,17 +2972,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130303237</v>
+        <v>130301029</v>
       </c>
       <c r="B22" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445744</v>
+        <v>445739</v>
       </c>
       <c r="R22" t="n">
-        <v>7026231</v>
+        <v>7026313</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3100,54 +3100,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130301029</v>
+        <v>130302646</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>97888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445739</v>
+        <v>445702</v>
       </c>
       <c r="R23" t="n">
-        <v>7026313</v>
+        <v>7026205</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3179,7 +3170,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3189,12 +3180,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,45 +3212,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130302646</v>
+        <v>130303237</v>
       </c>
       <c r="B24" t="n">
-        <v>97887</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445702</v>
+        <v>445744</v>
       </c>
       <c r="R24" t="n">
-        <v>7026205</v>
+        <v>7026231</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130300161</v>
+        <v>130300508</v>
       </c>
       <c r="B25" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3361,20 +3361,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445826</v>
+        <v>445754</v>
       </c>
       <c r="R25" t="n">
-        <v>7026362</v>
+        <v>7026380</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3403,7 +3412,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3413,7 +3422,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50 bålar på gammal gran (ca 175 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,22 +3442,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130300508</v>
+        <v>130300161</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3468,29 +3482,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445754</v>
+        <v>445826</v>
       </c>
       <c r="R26" t="n">
-        <v>7026380</v>
+        <v>7026362</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3519,7 +3524,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,12 +3534,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>50 bålar på gammal gran (ca 175 år) i gammal granskog</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3549,22 +3549,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130301166</v>
+        <v>130302477</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>91775</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,46 +3572,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445711</v>
+        <v>445700</v>
       </c>
       <c r="R27" t="n">
-        <v>7026280</v>
+        <v>7026308</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,12 +3641,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3670,22 +3661,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130300326</v>
+        <v>130301166</v>
       </c>
       <c r="B28" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3703,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3726,13 +3717,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445796</v>
+        <v>445711</v>
       </c>
       <c r="R28" t="n">
-        <v>7026382</v>
+        <v>7026280</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3761,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,12 +3762,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3796,17 +3787,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130302477</v>
+        <v>130300326</v>
       </c>
       <c r="B29" t="n">
-        <v>91774</v>
+        <v>79220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,37 +3805,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445700</v>
+        <v>445796</v>
       </c>
       <c r="R29" t="n">
-        <v>7026308</v>
+        <v>7026382</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,12 +3903,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3918,7 +3918,7 @@
         <v>130303489</v>
       </c>
       <c r="B30" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
         <v>130301943</v>
       </c>
       <c r="B31" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>130301011</v>
       </c>
       <c r="B32" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130302241</v>
+        <v>130302719</v>
       </c>
       <c r="B33" t="n">
-        <v>91774</v>
+        <v>79220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,42 +4261,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445762</v>
+        <v>445708</v>
       </c>
       <c r="R33" t="n">
-        <v>7026257</v>
+        <v>7026207</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4325,7 +4320,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4335,12 +4330,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,44 +4350,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130302719</v>
+        <v>130300852</v>
       </c>
       <c r="B34" t="n">
-        <v>79219</v>
+        <v>75198</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445708</v>
+        <v>445737</v>
       </c>
       <c r="R34" t="n">
-        <v>7026207</v>
+        <v>7026346</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4437,7 +4432,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4447,12 +4442,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4479,48 +4474,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300852</v>
+        <v>130302241</v>
       </c>
       <c r="B35" t="n">
-        <v>75197</v>
+        <v>91775</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445737</v>
+        <v>445762</v>
       </c>
       <c r="R35" t="n">
-        <v>7026346</v>
+        <v>7026257</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,22 +4579,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130302963</v>
+        <v>130301787</v>
       </c>
       <c r="B36" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445703</v>
+        <v>445675</v>
       </c>
       <c r="R36" t="n">
-        <v>7026235</v>
+        <v>7026220</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4712,10 +4712,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130301915</v>
+        <v>130302963</v>
       </c>
       <c r="B37" t="n">
-        <v>80324</v>
+        <v>79220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,37 +4723,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445762</v>
+        <v>445703</v>
       </c>
       <c r="R37" t="n">
-        <v>7026257</v>
+        <v>7026235</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4782,7 +4791,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4792,12 +4801,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4812,22 +4821,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301787</v>
+        <v>130301915</v>
       </c>
       <c r="B38" t="n">
-        <v>79219</v>
+        <v>80325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4835,46 +4844,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445675</v>
+        <v>445762</v>
       </c>
       <c r="R38" t="n">
-        <v>7026220</v>
+        <v>7026257</v>
       </c>
       <c r="S38" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,12 +4933,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4948,7 +4948,7 @@
         <v>130303099</v>
       </c>
       <c r="B39" t="n">
-        <v>78242</v>
+        <v>78243</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>130301433</v>
       </c>
       <c r="B40" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>130301690</v>
       </c>
       <c r="B41" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>August Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5299,7 +5299,7 @@
         <v>130719426</v>
       </c>
       <c r="B42" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130719785</v>
+        <v>130719742</v>
       </c>
       <c r="B43" t="n">
-        <v>78231</v>
+        <v>79220</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5419,34 +5419,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445739</v>
+        <v>445734</v>
       </c>
       <c r="R43" t="n">
-        <v>7026240</v>
+        <v>7026264</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5478,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5488,12 +5497,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5520,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130719742</v>
+        <v>130719248</v>
       </c>
       <c r="B44" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5550,7 +5559,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5564,13 +5573,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445734</v>
+        <v>445790</v>
       </c>
       <c r="R44" t="n">
-        <v>7026264</v>
+        <v>7026392</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5599,7 +5608,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5609,12 +5618,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5625,6 +5634,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5641,10 +5665,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130719248</v>
+        <v>130719785</v>
       </c>
       <c r="B45" t="n">
-        <v>79219</v>
+        <v>78232</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5652,46 +5676,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445790</v>
+        <v>445739</v>
       </c>
       <c r="R45" t="n">
-        <v>7026392</v>
+        <v>7026240</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5720,7 +5735,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5730,12 +5745,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5746,21 +5761,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5780,7 +5780,7 @@
         <v>130719929</v>
       </c>
       <c r="B46" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>130719892</v>
       </c>
       <c r="B47" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>130719486</v>
       </c>
       <c r="B48" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130719818</v>
       </c>
       <c r="B49" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>130719759</v>
       </c>
       <c r="B50" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>130719533</v>
       </c>
       <c r="B51" t="n">
-        <v>91770</v>
+        <v>91771</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>130719350</v>
       </c>
       <c r="B52" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130303417</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130303378</v>
+        <v>130301748</v>
       </c>
       <c r="B3" t="n">
-        <v>91775</v>
+        <v>80355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445813</v>
+        <v>445681</v>
       </c>
       <c r="R3" t="n">
-        <v>7026366</v>
+        <v>7026210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +901,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130301748</v>
+        <v>130303378</v>
       </c>
       <c r="B4" t="n">
-        <v>80354</v>
+        <v>91776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445681</v>
+        <v>445813</v>
       </c>
       <c r="R4" t="n">
-        <v>7026210</v>
+        <v>7026366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
         <v>130303406</v>
       </c>
       <c r="B5" t="n">
-        <v>78232</v>
+        <v>78233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>130301741</v>
       </c>
       <c r="B6" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,32 +1244,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130300210</v>
+        <v>130301523</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>80354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445816</v>
+        <v>445674</v>
       </c>
       <c r="R7" t="n">
-        <v>7026366</v>
+        <v>7026247</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1324,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,39 +1349,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130301523</v>
+        <v>130300210</v>
       </c>
       <c r="B8" t="n">
-        <v>80353</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445674</v>
+        <v>445816</v>
       </c>
       <c r="R8" t="n">
-        <v>7026247</v>
+        <v>7026366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
         <v>130303691</v>
       </c>
       <c r="B9" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>130300764</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130302348</v>
       </c>
       <c r="B11" t="n">
-        <v>91738</v>
+        <v>91739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>130303129</v>
       </c>
       <c r="B12" t="n">
-        <v>78232</v>
+        <v>78233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>130300940</v>
       </c>
       <c r="B13" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>130301447</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>130301555</v>
       </c>
       <c r="B15" t="n">
-        <v>97888</v>
+        <v>97891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130301089</v>
+        <v>130302398</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>78233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2304,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445726</v>
+        <v>445681</v>
       </c>
       <c r="R16" t="n">
-        <v>7026295</v>
+        <v>7026315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,10 +2405,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130302606</v>
+        <v>130301089</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445694</v>
+        <v>445726</v>
       </c>
       <c r="R17" t="n">
-        <v>7026212</v>
+        <v>7026295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,10 +2517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130302398</v>
+        <v>130302606</v>
       </c>
       <c r="B18" t="n">
-        <v>78232</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445681</v>
+        <v>445694</v>
       </c>
       <c r="R18" t="n">
-        <v>7026315</v>
+        <v>7026212</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,7 +2632,7 @@
         <v>130302583</v>
       </c>
       <c r="B19" t="n">
-        <v>83200</v>
+        <v>83201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>130303722</v>
       </c>
       <c r="B20" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>130300536</v>
       </c>
       <c r="B21" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2979,54 +2979,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130301029</v>
+        <v>130302646</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>97891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445739</v>
+        <v>445702</v>
       </c>
       <c r="R22" t="n">
-        <v>7026313</v>
+        <v>7026205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3058,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3068,12 +3059,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3100,45 +3091,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130302646</v>
+        <v>130303237</v>
       </c>
       <c r="B23" t="n">
-        <v>97888</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445702</v>
+        <v>445744</v>
       </c>
       <c r="R23" t="n">
-        <v>7026205</v>
+        <v>7026231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3180,12 +3180,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,10 +3212,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130303237</v>
+        <v>130301029</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445744</v>
+        <v>445739</v>
       </c>
       <c r="R24" t="n">
-        <v>7026231</v>
+        <v>7026313</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,10 +3333,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130300508</v>
+        <v>130300161</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3361,29 +3361,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445754</v>
+        <v>445826</v>
       </c>
       <c r="R25" t="n">
-        <v>7026380</v>
+        <v>7026362</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3412,7 +3403,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3422,12 +3413,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>50 bålar på gammal gran (ca 175 år) i gammal granskog</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3442,22 +3428,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130300161</v>
+        <v>130300508</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3482,20 +3468,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445826</v>
+        <v>445754</v>
       </c>
       <c r="R26" t="n">
-        <v>7026362</v>
+        <v>7026380</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3524,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3534,7 +3529,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>50 bålar på gammal gran (ca 175 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3549,22 +3549,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130302477</v>
+        <v>130301166</v>
       </c>
       <c r="B27" t="n">
-        <v>91775</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,37 +3572,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445700</v>
+        <v>445711</v>
       </c>
       <c r="R27" t="n">
-        <v>7026308</v>
+        <v>7026280</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3631,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,12 +3650,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,22 +3670,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130301166</v>
+        <v>130300326</v>
       </c>
       <c r="B28" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3712,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3717,13 +3726,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445711</v>
+        <v>445796</v>
       </c>
       <c r="R28" t="n">
-        <v>7026280</v>
+        <v>7026382</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3752,7 +3761,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,12 +3771,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,17 +3796,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130300326</v>
+        <v>130302477</v>
       </c>
       <c r="B29" t="n">
-        <v>79220</v>
+        <v>91776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3805,46 +3814,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445796</v>
+        <v>445700</v>
       </c>
       <c r="R29" t="n">
-        <v>7026382</v>
+        <v>7026308</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,12 +3903,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3918,7 +3918,7 @@
         <v>130303489</v>
       </c>
       <c r="B30" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>130301943</v>
       </c>
       <c r="B31" t="n">
-        <v>80326</v>
+        <v>80327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>130301011</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130302719</v>
+        <v>130302241</v>
       </c>
       <c r="B33" t="n">
-        <v>79220</v>
+        <v>91776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4261,37 +4261,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445708</v>
+        <v>445762</v>
       </c>
       <c r="R33" t="n">
-        <v>7026207</v>
+        <v>7026257</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4320,7 +4325,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4330,12 +4335,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4350,44 +4355,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130300852</v>
+        <v>130302719</v>
       </c>
       <c r="B34" t="n">
-        <v>75198</v>
+        <v>79221</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445737</v>
+        <v>445708</v>
       </c>
       <c r="R34" t="n">
-        <v>7026346</v>
+        <v>7026207</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4432,7 +4437,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4442,12 +4447,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4474,53 +4479,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130302241</v>
+        <v>130300852</v>
       </c>
       <c r="B35" t="n">
-        <v>91775</v>
+        <v>75199</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445762</v>
+        <v>445737</v>
       </c>
       <c r="R35" t="n">
-        <v>7026257</v>
+        <v>7026346</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,22 +4579,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130301787</v>
+        <v>130302963</v>
       </c>
       <c r="B36" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445675</v>
+        <v>445703</v>
       </c>
       <c r="R36" t="n">
-        <v>7026220</v>
+        <v>7026235</v>
       </c>
       <c r="S36" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4712,10 +4712,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130302963</v>
+        <v>130301787</v>
       </c>
       <c r="B37" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4756,13 +4756,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445703</v>
+        <v>445675</v>
       </c>
       <c r="R37" t="n">
-        <v>7026235</v>
+        <v>7026220</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4836,7 +4836,7 @@
         <v>130301915</v>
       </c>
       <c r="B38" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>130303099</v>
       </c>
       <c r="B39" t="n">
-        <v>78243</v>
+        <v>78244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>130301433</v>
       </c>
       <c r="B40" t="n">
-        <v>79691</v>
+        <v>79692</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>130301690</v>
       </c>
       <c r="B41" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>August Nordin, Emil Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5299,7 +5299,7 @@
         <v>130719426</v>
       </c>
       <c r="B42" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>130719742</v>
       </c>
       <c r="B43" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>130719248</v>
       </c>
       <c r="B44" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>130719785</v>
       </c>
       <c r="B45" t="n">
-        <v>78232</v>
+        <v>78233</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>130719929</v>
       </c>
       <c r="B46" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>130719892</v>
       </c>
       <c r="B47" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>130719486</v>
       </c>
       <c r="B48" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>130719818</v>
       </c>
       <c r="B49" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>130719759</v>
       </c>
       <c r="B50" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>130719533</v>
       </c>
       <c r="B51" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         <v>130719350</v>
       </c>
       <c r="B52" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6633,6 +6633,3183 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130839076</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78233</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>445706</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7026203</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130839080</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>445706</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7026203</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gammal gran i gles gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130838040</v>
+      </c>
+      <c r="B55" t="n">
+        <v>83206</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>445709</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7026357</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130838768</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>445697</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7026283</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130838099</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>445679</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7026381</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På död gammal gran</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130838346</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91796</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>445675</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7026326</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På levande gran i björkrik granskog</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130838225</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>445632</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7026388</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gammal gran i gles skog nära källa</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130839371</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>445780</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7026357</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På gammal gran (ca 200 år) i gles gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130839417</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>445781</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7026373</v>
+      </c>
+      <c r="S61" t="n">
+        <v>7</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130837289</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>445777</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7026331</v>
+      </c>
+      <c r="S62" t="n">
+        <v>6</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130838554</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>445665</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7026277</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gammal levande gran i björkrik granskog</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130837438</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78233</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>445741</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7026328</v>
+      </c>
+      <c r="S64" t="n">
+        <v>6</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130837548</v>
+      </c>
+      <c r="B65" t="n">
+        <v>83201</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>445740</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7026322</v>
+      </c>
+      <c r="S65" t="n">
+        <v>8</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130837393</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>445769</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7026332</v>
+      </c>
+      <c r="S66" t="n">
+        <v>8</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal levande gran (ca 175 år, 25 cm dbh) i gammal granskog, längsta bål 40 cm</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130839350</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>445790</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7026340</v>
+      </c>
+      <c r="S67" t="n">
+        <v>6</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130839110</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>445730</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7026205</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På gammal klen död gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130837316</v>
+      </c>
+      <c r="B69" t="n">
+        <v>83201</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>445777</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7026331</v>
+      </c>
+      <c r="S69" t="n">
+        <v>6</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130838077</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78233</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>445709</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7026369</v>
+      </c>
+      <c r="S70" t="n">
+        <v>6</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (ca 200 år, 15 cm dbh) i gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>130838158</v>
+      </c>
+      <c r="B71" t="n">
+        <v>83201</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>445638</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7026382</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog, nära källa</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>130838918</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>445653</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7026235</v>
+      </c>
+      <c r="S72" t="n">
+        <v>8</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gammal levande gran (ca 200 år) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>130839401</v>
+      </c>
+      <c r="B73" t="n">
+        <v>83201</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>445781</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7026373</v>
+      </c>
+      <c r="S73" t="n">
+        <v>7</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>130839069</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79477</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>445706</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7026203</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På död gren på gammal levande gran</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>130839071</v>
+      </c>
+      <c r="B75" t="n">
+        <v>83201</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>445706</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7026203</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>130837541</v>
+      </c>
+      <c r="B76" t="n">
+        <v>75199</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>445740</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7026322</v>
+      </c>
+      <c r="S76" t="n">
+        <v>8</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På tunna kvistar vid basen på gammal levande gran</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>130837733</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>445720</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7026343</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gammal död gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>130838833</v>
+      </c>
+      <c r="B78" t="n">
+        <v>89169</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>510</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>445685</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7026259</v>
+      </c>
+      <c r="S78" t="n">
+        <v>4</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På granlåga i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>130839413</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78233</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>445781</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7026373</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>130839277</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>445728</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7026301</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -796,32 +796,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130301748</v>
+        <v>130303378</v>
       </c>
       <c r="B3" t="n">
-        <v>80355</v>
+        <v>91776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445681</v>
+        <v>445813</v>
       </c>
       <c r="R3" t="n">
-        <v>7026210</v>
+        <v>7026366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,39 +901,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130303378</v>
+        <v>130301748</v>
       </c>
       <c r="B4" t="n">
-        <v>91776</v>
+        <v>80355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445813</v>
+        <v>445681</v>
       </c>
       <c r="R4" t="n">
-        <v>7026366</v>
+        <v>7026210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130303406</v>
+        <v>130301741</v>
       </c>
       <c r="B5" t="n">
-        <v>78233</v>
+        <v>83201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445827</v>
+        <v>445718</v>
       </c>
       <c r="R5" t="n">
-        <v>7026371</v>
+        <v>7026281</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130301741</v>
+        <v>130303406</v>
       </c>
       <c r="B6" t="n">
-        <v>83201</v>
+        <v>78233</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445718</v>
+        <v>445827</v>
       </c>
       <c r="R6" t="n">
-        <v>7026281</v>
+        <v>7026371</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,60 +1232,74 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130301523</v>
+        <v>130303691</v>
       </c>
       <c r="B7" t="n">
-        <v>80354</v>
+        <v>98974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445674</v>
+        <v>445781</v>
       </c>
       <c r="R7" t="n">
-        <v>7026247</v>
+        <v>7026394</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,12 +1338,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,7 +1363,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1468,62 +1482,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130303691</v>
+        <v>130301523</v>
       </c>
       <c r="B9" t="n">
-        <v>98974</v>
+        <v>80354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445781</v>
+        <v>445674</v>
       </c>
       <c r="R9" t="n">
-        <v>7026394</v>
+        <v>7026247</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1939,54 +1939,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130300940</v>
+        <v>130301555</v>
       </c>
       <c r="B13" t="n">
-        <v>79221</v>
+        <v>97891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445746</v>
+        <v>445699</v>
       </c>
       <c r="R13" t="n">
-        <v>7026325</v>
+        <v>7026231</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,12 +2019,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,14 +2044,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130301447</v>
+        <v>130300940</v>
       </c>
       <c r="B14" t="n">
         <v>79221</v>
@@ -2104,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445671</v>
+        <v>445746</v>
       </c>
       <c r="R14" t="n">
-        <v>7026257</v>
+        <v>7026325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,12 +2140,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 200 år) i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,45 +2172,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130301555</v>
+        <v>130301447</v>
       </c>
       <c r="B15" t="n">
-        <v>97891</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445699</v>
+        <v>445671</v>
       </c>
       <c r="R15" t="n">
-        <v>7026231</v>
+        <v>7026257</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På gammal gran (ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2979,45 +2979,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130302646</v>
+        <v>130303237</v>
       </c>
       <c r="B22" t="n">
-        <v>97891</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445702</v>
+        <v>445744</v>
       </c>
       <c r="R22" t="n">
-        <v>7026205</v>
+        <v>7026231</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3058,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,12 +3068,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3091,7 +3100,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130303237</v>
+        <v>130301029</v>
       </c>
       <c r="B23" t="n">
         <v>79221</v>
@@ -3121,7 +3130,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3135,10 +3144,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445744</v>
+        <v>445739</v>
       </c>
       <c r="R23" t="n">
-        <v>7026231</v>
+        <v>7026313</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3170,7 +3179,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3180,12 +3189,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,54 +3221,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130301029</v>
+        <v>130302646</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>97891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445739</v>
+        <v>445702</v>
       </c>
       <c r="R24" t="n">
-        <v>7026313</v>
+        <v>7026205</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3561,42 +3561,47 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130301166</v>
+        <v>130303489</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>98974</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3605,13 +3610,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445711</v>
+        <v>445824</v>
       </c>
       <c r="R27" t="n">
-        <v>7026280</v>
+        <v>7026381</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,12 +3655,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3675,17 +3680,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130300326</v>
+        <v>130302477</v>
       </c>
       <c r="B28" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3693,46 +3698,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445796</v>
+        <v>445700</v>
       </c>
       <c r="R28" t="n">
-        <v>7026382</v>
+        <v>7026308</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3761,7 +3757,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3771,12 +3767,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3791,22 +3787,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130302477</v>
+        <v>130301166</v>
       </c>
       <c r="B29" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,37 +3810,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445700</v>
+        <v>445711</v>
       </c>
       <c r="R29" t="n">
-        <v>7026308</v>
+        <v>7026280</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3873,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3883,12 +3888,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,59 +3908,54 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130303489</v>
+        <v>130300326</v>
       </c>
       <c r="B30" t="n">
-        <v>98974</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3964,13 +3964,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445824</v>
+        <v>445796</v>
       </c>
       <c r="R30" t="n">
-        <v>7026381</v>
+        <v>7026382</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130301787</v>
+        <v>130301915</v>
       </c>
       <c r="B37" t="n">
-        <v>79221</v>
+        <v>80326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4723,46 +4723,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445675</v>
+        <v>445762</v>
       </c>
       <c r="R37" t="n">
-        <v>7026220</v>
+        <v>7026257</v>
       </c>
       <c r="S37" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4791,7 +4782,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4801,12 +4792,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,22 +4812,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301915</v>
+        <v>130301787</v>
       </c>
       <c r="B38" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,37 +4835,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445762</v>
+        <v>445675</v>
       </c>
       <c r="R38" t="n">
-        <v>7026257</v>
+        <v>7026220</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4933,12 +4933,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -7649,7 +7649,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130837289</v>
+        <v>130838554</v>
       </c>
       <c r="B62" t="n">
         <v>79221</v>
@@ -7677,29 +7677,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445777</v>
+        <v>445665</v>
       </c>
       <c r="R62" t="n">
-        <v>7026331</v>
+        <v>7026277</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7728,7 +7719,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7738,12 +7729,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>På gammal levande gran i björkrik granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7770,7 +7761,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130838554</v>
+        <v>130837289</v>
       </c>
       <c r="B63" t="n">
         <v>79221</v>
@@ -7798,20 +7789,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445665</v>
+        <v>445777</v>
       </c>
       <c r="R63" t="n">
-        <v>7026277</v>
+        <v>7026331</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gammal levande gran i björkrik granskog</t>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7994,10 +7994,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130837548</v>
+        <v>130839350</v>
       </c>
       <c r="B65" t="n">
-        <v>83201</v>
+        <v>79221</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8005,21 +8005,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8029,13 +8029,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445740</v>
+        <v>445790</v>
       </c>
       <c r="R65" t="n">
-        <v>7026322</v>
+        <v>7026340</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8106,10 +8106,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130837393</v>
+        <v>130837548</v>
       </c>
       <c r="B66" t="n">
-        <v>79221</v>
+        <v>83201</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8117,43 +8117,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445769</v>
+        <v>445740</v>
       </c>
       <c r="R66" t="n">
-        <v>7026332</v>
+        <v>7026322</v>
       </c>
       <c r="S66" t="n">
         <v>8</v>
@@ -8185,7 +8176,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8195,12 +8186,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 175 år, 25 cm dbh) i gammal granskog, längsta bål 40 cm</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8227,7 +8218,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130839350</v>
+        <v>130837393</v>
       </c>
       <c r="B67" t="n">
         <v>79221</v>
@@ -8255,20 +8246,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445790</v>
+        <v>445769</v>
       </c>
       <c r="R67" t="n">
-        <v>7026340</v>
+        <v>7026332</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal levande gran (ca 175 år, 25 cm dbh) i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9244,32 +9244,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130837541</v>
+        <v>130839413</v>
       </c>
       <c r="B76" t="n">
-        <v>75199</v>
+        <v>78233</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9279,13 +9279,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445740</v>
+        <v>445781</v>
       </c>
       <c r="R76" t="n">
-        <v>7026322</v>
+        <v>7026373</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På tunna kvistar vid basen på gammal levande gran</t>
+          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9356,10 +9356,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130837733</v>
+        <v>130838833</v>
       </c>
       <c r="B77" t="n">
-        <v>79221</v>
+        <v>89169</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9367,21 +9367,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9391,13 +9391,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445720</v>
+        <v>445685</v>
       </c>
       <c r="R77" t="n">
-        <v>7026343</v>
+        <v>7026259</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gammal död gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9468,10 +9468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130838833</v>
+        <v>130837733</v>
       </c>
       <c r="B78" t="n">
-        <v>89169</v>
+        <v>79221</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9479,21 +9479,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9503,13 +9503,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445685</v>
+        <v>445720</v>
       </c>
       <c r="R78" t="n">
-        <v>7026259</v>
+        <v>7026343</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9580,32 +9580,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130839413</v>
+        <v>130837541</v>
       </c>
       <c r="B79" t="n">
-        <v>78233</v>
+        <v>75199</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9615,13 +9615,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445781</v>
+        <v>445740</v>
       </c>
       <c r="R79" t="n">
-        <v>7026373</v>
+        <v>7026322</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
+          <t>På tunna kvistar vid basen på gammal levande gran</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -6860,10 +6860,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130838040</v>
+        <v>130838768</v>
       </c>
       <c r="B55" t="n">
-        <v>83206</v>
+        <v>79221</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6871,21 +6871,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445709</v>
+        <v>445697</v>
       </c>
       <c r="R55" t="n">
-        <v>7026357</v>
+        <v>7026283</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6972,10 +6972,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130838768</v>
+        <v>130838040</v>
       </c>
       <c r="B56" t="n">
-        <v>79221</v>
+        <v>83206</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445697</v>
+        <v>445709</v>
       </c>
       <c r="R56" t="n">
-        <v>7026283</v>
+        <v>7026357</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -9244,10 +9244,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130839413</v>
+        <v>130837733</v>
       </c>
       <c r="B76" t="n">
-        <v>78233</v>
+        <v>79221</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9255,21 +9255,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9279,13 +9279,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445781</v>
+        <v>445720</v>
       </c>
       <c r="R76" t="n">
-        <v>7026373</v>
+        <v>7026343</v>
       </c>
       <c r="S76" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
+          <t>På gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9356,32 +9356,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130838833</v>
+        <v>130837541</v>
       </c>
       <c r="B77" t="n">
-        <v>89169</v>
+        <v>75199</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>6428</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9391,13 +9391,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445685</v>
+        <v>445740</v>
       </c>
       <c r="R77" t="n">
-        <v>7026259</v>
+        <v>7026322</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På tunna kvistar vid basen på gammal levande gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9468,10 +9468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130837733</v>
+        <v>130838833</v>
       </c>
       <c r="B78" t="n">
-        <v>79221</v>
+        <v>89169</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9479,21 +9479,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9503,13 +9503,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445720</v>
+        <v>445685</v>
       </c>
       <c r="R78" t="n">
-        <v>7026343</v>
+        <v>7026259</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gammal död gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9580,32 +9580,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130837541</v>
+        <v>130839413</v>
       </c>
       <c r="B79" t="n">
-        <v>75199</v>
+        <v>78233</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9615,13 +9615,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445740</v>
+        <v>445781</v>
       </c>
       <c r="R79" t="n">
-        <v>7026322</v>
+        <v>7026373</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På tunna kvistar vid basen på gammal levande gran</t>
+          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -6860,10 +6860,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130838768</v>
+        <v>130838040</v>
       </c>
       <c r="B55" t="n">
-        <v>79221</v>
+        <v>83206</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6871,21 +6871,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445697</v>
+        <v>445709</v>
       </c>
       <c r="R55" t="n">
-        <v>7026283</v>
+        <v>7026357</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6972,10 +6972,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130838040</v>
+        <v>130838768</v>
       </c>
       <c r="B56" t="n">
-        <v>83206</v>
+        <v>79221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445709</v>
+        <v>445697</v>
       </c>
       <c r="R56" t="n">
-        <v>7026357</v>
+        <v>7026283</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8339,10 +8339,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130839110</v>
+        <v>130837316</v>
       </c>
       <c r="B68" t="n">
-        <v>79221</v>
+        <v>83201</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8350,46 +8350,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445730</v>
+        <v>445777</v>
       </c>
       <c r="R68" t="n">
-        <v>7026205</v>
+        <v>7026331</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8418,7 +8409,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8428,12 +8419,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gammal klen död gran i gammal granskog</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8460,10 +8451,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130837316</v>
+        <v>130839110</v>
       </c>
       <c r="B69" t="n">
-        <v>83201</v>
+        <v>79221</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8471,37 +8462,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445777</v>
+        <v>445730</v>
       </c>
       <c r="R69" t="n">
-        <v>7026331</v>
+        <v>7026205</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal klen död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9468,10 +9468,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130838833</v>
+        <v>130839413</v>
       </c>
       <c r="B78" t="n">
-        <v>89169</v>
+        <v>78233</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9479,21 +9479,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9503,13 +9503,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445685</v>
+        <v>445781</v>
       </c>
       <c r="R78" t="n">
-        <v>7026259</v>
+        <v>7026373</v>
       </c>
       <c r="S78" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9580,10 +9580,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130839413</v>
+        <v>130838833</v>
       </c>
       <c r="B79" t="n">
-        <v>78233</v>
+        <v>89169</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9591,21 +9591,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228579</v>
+        <v>510</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9615,13 +9615,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445781</v>
+        <v>445685</v>
       </c>
       <c r="R79" t="n">
-        <v>7026373</v>
+        <v>7026259</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -6860,10 +6860,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130838768</v>
+        <v>130838040</v>
       </c>
       <c r="B55" t="n">
-        <v>79244</v>
+        <v>83229</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6871,21 +6871,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445697</v>
+        <v>445709</v>
       </c>
       <c r="R55" t="n">
-        <v>7026283</v>
+        <v>7026357</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6972,10 +6972,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130838040</v>
+        <v>130838768</v>
       </c>
       <c r="B56" t="n">
-        <v>83229</v>
+        <v>79244</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445709</v>
+        <v>445697</v>
       </c>
       <c r="R56" t="n">
-        <v>7026357</v>
+        <v>7026283</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7042,7 +7042,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7994,10 +7994,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130839350</v>
+        <v>130837548</v>
       </c>
       <c r="B65" t="n">
-        <v>79244</v>
+        <v>83224</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8005,21 +8005,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8029,13 +8029,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445790</v>
+        <v>445740</v>
       </c>
       <c r="R65" t="n">
-        <v>7026340</v>
+        <v>7026322</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8106,10 +8106,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130837548</v>
+        <v>130839350</v>
       </c>
       <c r="B66" t="n">
-        <v>83224</v>
+        <v>79244</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8117,21 +8117,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8141,13 +8141,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445740</v>
+        <v>445790</v>
       </c>
       <c r="R66" t="n">
-        <v>7026322</v>
+        <v>7026340</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9244,32 +9244,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130838833</v>
+        <v>130837541</v>
       </c>
       <c r="B76" t="n">
-        <v>89194</v>
+        <v>75222</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>510</v>
+        <v>6428</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9279,13 +9279,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445685</v>
+        <v>445740</v>
       </c>
       <c r="R76" t="n">
-        <v>7026259</v>
+        <v>7026322</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På tunna kvistar vid basen på gammal levande gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9356,10 +9356,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130837733</v>
+        <v>130838833</v>
       </c>
       <c r="B77" t="n">
-        <v>79244</v>
+        <v>89194</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9367,21 +9367,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9391,13 +9391,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445720</v>
+        <v>445685</v>
       </c>
       <c r="R77" t="n">
-        <v>7026343</v>
+        <v>7026259</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På gammal död gran i gammal granskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9468,32 +9468,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130837541</v>
+        <v>130837733</v>
       </c>
       <c r="B78" t="n">
-        <v>75222</v>
+        <v>79244</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9503,13 +9503,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445740</v>
+        <v>445720</v>
       </c>
       <c r="R78" t="n">
-        <v>7026322</v>
+        <v>7026343</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9548,12 +9548,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På tunna kvistar vid basen på gammal levande gran</t>
+          <t>På gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -9816,7 +9816,7 @@
         <v>131074382</v>
       </c>
       <c r="B81" t="n">
-        <v>57988</v>
+        <v>57990</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -9816,7 +9816,7 @@
         <v>131074382</v>
       </c>
       <c r="B81" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -9816,7 +9816,7 @@
         <v>131074382</v>
       </c>
       <c r="B81" t="n">
-        <v>57991</v>
+        <v>57992</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130303417</v>
+        <v>130303099</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445827</v>
+        <v>445734</v>
       </c>
       <c r="R2" t="n">
-        <v>7026371</v>
+        <v>7026229</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på undersidan av död gren på gammal levande gran (ca 200 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130303378</v>
+        <v>130838833</v>
       </c>
       <c r="B3" t="n">
-        <v>91776</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445813</v>
+        <v>445685</v>
       </c>
       <c r="R3" t="n">
-        <v>7026366</v>
+        <v>7026259</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,27 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga i gammal gransumpskog</t>
+          <t>På granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130301748</v>
+        <v>130300541</v>
       </c>
       <c r="B4" t="n">
-        <v>80355</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445681</v>
+        <v>445737</v>
       </c>
       <c r="R4" t="n">
-        <v>7026210</v>
+        <v>7026387</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På död gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Ludvig Nordin, Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130301741</v>
+        <v>130719486</v>
       </c>
       <c r="B5" t="n">
-        <v>83201</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445718</v>
+        <v>445689</v>
       </c>
       <c r="R5" t="n">
-        <v>7026281</v>
+        <v>7026360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>På granhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130303406</v>
+        <v>130719533</v>
       </c>
       <c r="B6" t="n">
-        <v>78233</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445827</v>
+        <v>445674</v>
       </c>
       <c r="R6" t="n">
-        <v>7026371</v>
+        <v>7026358</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,27 +1188,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granhögstubbe (40 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,47 +1235,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130303691</v>
+        <v>130302241</v>
       </c>
       <c r="B7" t="n">
-        <v>98974</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1293,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445781</v>
+        <v>445762</v>
       </c>
       <c r="R7" t="n">
-        <v>7026394</v>
+        <v>7026257</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1328,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,12 +1320,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,22 +1340,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130300210</v>
+        <v>130302477</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445816</v>
+        <v>445700</v>
       </c>
       <c r="R8" t="n">
-        <v>7026366</v>
+        <v>7026308</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,12 +1432,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,44 +1452,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130301523</v>
+        <v>130303378</v>
       </c>
       <c r="B9" t="n">
-        <v>80354</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445674</v>
+        <v>445813</v>
       </c>
       <c r="R9" t="n">
-        <v>7026247</v>
+        <v>7026366</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,12 +1544,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På granlåga i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,17 +1569,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130300764</v>
+        <v>130838040</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>83312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,46 +1587,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445754</v>
+        <v>445709</v>
       </c>
       <c r="R10" t="n">
-        <v>7026359</v>
+        <v>7026357</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,27 +1641,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal död gran</t>
+          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,44 +1676,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130302348</v>
+        <v>130301433</v>
       </c>
       <c r="B11" t="n">
-        <v>91739</v>
+        <v>79798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1797</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445688</v>
+        <v>445678</v>
       </c>
       <c r="R11" t="n">
-        <v>7026324</v>
+        <v>7026239</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,12 +1768,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130303129</v>
+        <v>130301943</v>
       </c>
       <c r="B12" t="n">
-        <v>78233</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445734</v>
+        <v>445762</v>
       </c>
       <c r="R12" t="n">
-        <v>7026229</v>
+        <v>7026257</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1897,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,12 +1880,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal gransumpskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,22 +1900,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130301555</v>
+        <v>130302348</v>
       </c>
       <c r="B13" t="n">
-        <v>97891</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221063</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1974,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445699</v>
+        <v>445688</v>
       </c>
       <c r="R13" t="n">
-        <v>7026231</v>
+        <v>7026324</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,12 +1992,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal sumpgranskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,26 +2012,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130300940</v>
+        <v>130300161</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2079,29 +2052,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445746</v>
+        <v>445826</v>
       </c>
       <c r="R14" t="n">
-        <v>7026325</v>
+        <v>7026362</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2130,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,12 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal levande gran i gammal granskog</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,26 +2119,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130301447</v>
+        <v>130300210</v>
       </c>
       <c r="B15" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2200,26 +2159,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445671</v>
+        <v>445816</v>
       </c>
       <c r="R15" t="n">
-        <v>7026257</v>
+        <v>7026366</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,12 +2211,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 200 år) i gammal granskog</t>
+          <t>På gammal gran (ca 150 år) i gammal klenvuxen granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,52 +2236,61 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130302398</v>
+        <v>130300326</v>
       </c>
       <c r="B16" t="n">
-        <v>78233</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445681</v>
+        <v>445796</v>
       </c>
       <c r="R16" t="n">
-        <v>7026315</v>
+        <v>7026382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,12 +2332,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
+          <t>På gammal levande gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,21 +2357,21 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130301089</v>
+        <v>130300508</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2433,17 +2392,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445726</v>
+        <v>445754</v>
       </c>
       <c r="R17" t="n">
-        <v>7026295</v>
+        <v>7026380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2443,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,12 +2453,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
+          <t>50 bålar på gammal gran (ca 175 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,14 +2485,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130302606</v>
+        <v>130300764</v>
       </c>
       <c r="B18" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2545,20 +2513,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445694</v>
+        <v>445754</v>
       </c>
       <c r="R18" t="n">
-        <v>7026212</v>
+        <v>7026359</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2587,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,12 +2574,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal död gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,57 +2594,66 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Emil Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130302583</v>
+        <v>130300940</v>
       </c>
       <c r="B19" t="n">
-        <v>83201</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445687</v>
+        <v>445746</v>
       </c>
       <c r="R19" t="n">
-        <v>7026235</v>
+        <v>7026325</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,12 +2695,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130303722</v>
+        <v>130301011</v>
       </c>
       <c r="B20" t="n">
-        <v>98974</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,48 +2738,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445791</v>
+        <v>445774</v>
       </c>
       <c r="R20" t="n">
-        <v>7026379</v>
+        <v>7026314</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,24 +2795,9 @@
           <t>2025-12-26</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,57 +2812,66 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Emil Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130300536</v>
+        <v>130301029</v>
       </c>
       <c r="B21" t="n">
-        <v>97845</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445736</v>
+        <v>445739</v>
       </c>
       <c r="R21" t="n">
-        <v>7026373</v>
+        <v>7026313</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,12 +2913,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,14 +2945,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130303237</v>
+        <v>130301089</v>
       </c>
       <c r="B22" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3007,26 +2973,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445744</v>
+        <v>445726</v>
       </c>
       <c r="R22" t="n">
-        <v>7026231</v>
+        <v>7026295</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3058,7 +3015,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3068,12 +3025,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal tall (200 år) i gammal granskog på sumpig mark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3100,14 +3057,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130301029</v>
+        <v>130301166</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3130,7 +3087,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3144,13 +3101,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445739</v>
+        <v>445711</v>
       </c>
       <c r="R23" t="n">
-        <v>7026313</v>
+        <v>7026280</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3179,7 +3136,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3189,12 +3146,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på 200 år gammal levande gran i gammal granskog</t>
+          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,45 +3178,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130302646</v>
+        <v>130301447</v>
       </c>
       <c r="B24" t="n">
-        <v>97891</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Michx.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445702</v>
+        <v>445671</v>
       </c>
       <c r="R24" t="n">
-        <v>7026205</v>
+        <v>7026257</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3291,7 +3257,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3301,12 +3267,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal granskog</t>
+          <t>På gammal gran (ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,14 +3299,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130300161</v>
+        <v>130301787</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3361,20 +3327,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445826</v>
+        <v>445675</v>
       </c>
       <c r="R25" t="n">
-        <v>7026362</v>
+        <v>7026220</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3403,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3413,7 +3388,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,26 +3408,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130300508</v>
+        <v>130302606</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3468,26 +3448,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445754</v>
+        <v>445694</v>
       </c>
       <c r="R26" t="n">
-        <v>7026380</v>
+        <v>7026212</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,12 +3500,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>50 bålar på gammal gran (ca 175 år) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3561,10 +3532,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130303489</v>
+        <v>130302719</v>
       </c>
       <c r="B27" t="n">
-        <v>98974</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,51 +3543,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445824</v>
+        <v>445708</v>
       </c>
       <c r="R27" t="n">
-        <v>7026381</v>
+        <v>7026207</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3645,7 +3602,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,12 +3612,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>3 vinterståndare på marken i gammal granskog</t>
+          <t>På gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3680,55 +3637,64 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130302477</v>
+        <v>130302963</v>
       </c>
       <c r="B28" t="n">
-        <v>91776</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445700</v>
+        <v>445703</v>
       </c>
       <c r="R28" t="n">
-        <v>7026308</v>
+        <v>7026235</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3757,7 +3723,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3767,12 +3733,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt på gammal klen gran i gransumpskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,26 +3753,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130301166</v>
+        <v>130303237</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3843,13 +3809,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445711</v>
+        <v>445744</v>
       </c>
       <c r="R29" t="n">
-        <v>7026280</v>
+        <v>7026231</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,7 +3844,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,12 +3854,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 180 år) i gammal granskog (ca 150-200 år)</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3920,14 +3886,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130300326</v>
+        <v>130303417</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3950,7 +3916,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3964,10 +3930,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445796</v>
+        <v>445827</v>
       </c>
       <c r="R30" t="n">
-        <v>7026382</v>
+        <v>7026371</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3999,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,12 +3975,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal levande gran i gammal gransumpskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4034,52 +4000,61 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130301943</v>
+        <v>130719248</v>
       </c>
       <c r="B31" t="n">
-        <v>80327</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445762</v>
+        <v>445790</v>
       </c>
       <c r="R31" t="n">
-        <v>7026257</v>
+        <v>7026392</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4106,27 +4081,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4137,30 +4112,45 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130301011</v>
+        <v>130719350</v>
       </c>
       <c r="B32" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4181,17 +4171,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445774</v>
+        <v>445746</v>
       </c>
       <c r="R32" t="n">
-        <v>7026314</v>
+        <v>7026368</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4218,12 +4217,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Draperat på 200-årig gammal levande gran i gammal granskog, längsta bål 60 cm</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4234,69 +4248,79 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130302241</v>
+        <v>130719426</v>
       </c>
       <c r="B33" t="n">
-        <v>91776</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445762</v>
+        <v>445709</v>
       </c>
       <c r="R33" t="n">
-        <v>7026257</v>
+        <v>7026371</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4320,27 +4344,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal levande gran (42 cm dbh, ca 170 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,26 +4379,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130302719</v>
+        <v>130719742</v>
       </c>
       <c r="B34" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4395,17 +4419,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445708</v>
+        <v>445734</v>
       </c>
       <c r="R34" t="n">
-        <v>7026207</v>
+        <v>7026264</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4432,27 +4465,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal gransumpskog</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4479,48 +4512,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130300852</v>
+        <v>130719759</v>
       </c>
       <c r="B35" t="n">
-        <v>75199</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445737</v>
+        <v>445728</v>
       </c>
       <c r="R35" t="n">
-        <v>7026346</v>
+        <v>7026253</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4544,27 +4586,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran</t>
+          <t>40 bålar på 200-årig tall i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4575,6 +4617,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4591,14 +4648,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130302963</v>
+        <v>130719818</v>
       </c>
       <c r="B36" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4621,7 +4678,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4635,10 +4692,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445703</v>
+        <v>445747</v>
       </c>
       <c r="R36" t="n">
-        <v>7026235</v>
+        <v>7026270</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4665,27 +4722,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på gammal klen gran i gransumpskog</t>
+          <t>Rikligt på gammal levande gran (24 cm dbh, ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4712,48 +4769,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130301915</v>
+        <v>130719892</v>
       </c>
       <c r="B37" t="n">
-        <v>80326</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445762</v>
+        <v>445759</v>
       </c>
       <c r="R37" t="n">
-        <v>7026257</v>
+        <v>7026307</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4777,27 +4843,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>1000 bålar fördelat på 10 gamla granar i gammal granskog, längsta bållängd 70 cm</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4812,26 +4878,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130301787</v>
+        <v>130719929</v>
       </c>
       <c r="B38" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4868,13 +4934,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445675</v>
+        <v>445789</v>
       </c>
       <c r="R38" t="n">
-        <v>7026220</v>
+        <v>7026327</v>
       </c>
       <c r="S38" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4898,27 +4964,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal levande gran (40 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4945,48 +5011,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130303099</v>
+        <v>130837289</v>
       </c>
       <c r="B39" t="n">
-        <v>78244</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445734</v>
+        <v>445777</v>
       </c>
       <c r="R39" t="n">
-        <v>7026229</v>
+        <v>7026331</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5010,27 +5085,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på undersidan av död gren på gammal levande gran (ca 200 år) i gammal gransumpskog</t>
+          <t>Rikligt på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5057,48 +5132,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130301433</v>
+        <v>130837393</v>
       </c>
       <c r="B40" t="n">
-        <v>79692</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445678</v>
+        <v>445769</v>
       </c>
       <c r="R40" t="n">
-        <v>7026239</v>
+        <v>7026332</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5122,27 +5206,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>Rikligt på gammal levande gran (ca 175 år, 25 cm dbh) i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5157,44 +5241,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130301690</v>
+        <v>130837733</v>
       </c>
       <c r="B41" t="n">
-        <v>80326</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5204,10 +5288,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445682</v>
+        <v>445720</v>
       </c>
       <c r="R41" t="n">
-        <v>7026217</v>
+        <v>7026343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5234,27 +5318,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal sumpgranskog</t>
+          <t>På gammal död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5265,21 +5349,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5289,21 +5358,21 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130719426</v>
+        <v>130838099</v>
       </c>
       <c r="B42" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5331,10 +5400,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445709</v>
+        <v>445679</v>
       </c>
       <c r="R42" t="n">
-        <v>7026371</v>
+        <v>7026381</v>
       </c>
       <c r="S42" t="n">
         <v>6</v>
@@ -5361,27 +5430,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal levande gran (42 cm dbh, ca 170 år) i gammal granskog</t>
+          <t>På död gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5408,14 +5477,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130719248</v>
+        <v>130838225</v>
       </c>
       <c r="B43" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5436,29 +5505,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445790</v>
+        <v>445632</v>
       </c>
       <c r="R43" t="n">
-        <v>7026392</v>
+        <v>7026388</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5482,27 +5542,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (13 cm dbh, ca 175 år) i gammal granskog</t>
+          <t>På gammal gran i gles skog nära källa</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5513,21 +5573,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5544,32 +5589,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130719785</v>
+        <v>130838554</v>
       </c>
       <c r="B44" t="n">
-        <v>78255</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5579,10 +5624,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445739</v>
+        <v>445665</v>
       </c>
       <c r="R44" t="n">
-        <v>7026240</v>
+        <v>7026277</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5609,27 +5654,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal levande gran i björkrik granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5656,14 +5701,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130719742</v>
+        <v>130838768</v>
       </c>
       <c r="B45" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5684,26 +5729,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445734</v>
+        <v>445697</v>
       </c>
       <c r="R45" t="n">
-        <v>7026264</v>
+        <v>7026283</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5730,27 +5766,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5777,14 +5813,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130719929</v>
+        <v>130838918</v>
       </c>
       <c r="B46" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5805,29 +5841,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445789</v>
+        <v>445653</v>
       </c>
       <c r="R46" t="n">
-        <v>7026327</v>
+        <v>7026235</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5851,27 +5878,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>På gammal levande gran (ca 200 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5898,14 +5925,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130719892</v>
+        <v>130839080</v>
       </c>
       <c r="B47" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5926,26 +5953,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445759</v>
+        <v>445706</v>
       </c>
       <c r="R47" t="n">
-        <v>7026307</v>
+        <v>7026203</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5972,27 +5990,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1000 bålar fördelat på 10 gamla granar i gammal granskog, längsta bållängd 70 cm</t>
+          <t>På gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6019,48 +6037,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130719486</v>
+        <v>130839110</v>
       </c>
       <c r="B48" t="n">
-        <v>91804</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445689</v>
+        <v>445730</v>
       </c>
       <c r="R48" t="n">
-        <v>7026360</v>
+        <v>7026205</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6084,27 +6111,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På granhögstubbe i gammal granskog</t>
+          <t>På gammal klen död gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6131,14 +6158,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130719818</v>
+        <v>130839277</v>
       </c>
       <c r="B49" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -6161,7 +6188,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6175,13 +6202,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445747</v>
+        <v>445728</v>
       </c>
       <c r="R49" t="n">
-        <v>7026270</v>
+        <v>7026301</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6205,27 +6232,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (24 cm dbh, ca 200 år) i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6252,14 +6279,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130719759</v>
+        <v>130839350</v>
       </c>
       <c r="B50" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -6280,29 +6307,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445728</v>
+        <v>445790</v>
       </c>
       <c r="R50" t="n">
-        <v>7026253</v>
+        <v>7026340</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6326,27 +6344,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>40 bålar på 200-årig tall i gles gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6357,21 +6375,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6388,45 +6391,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130719533</v>
+        <v>130839371</v>
       </c>
       <c r="B51" t="n">
-        <v>91804</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445674</v>
+        <v>445780</v>
       </c>
       <c r="R51" t="n">
-        <v>7026358</v>
+        <v>7026357</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6453,27 +6465,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På granhögstubbe (40 cm dbh) i gammal granskog</t>
+          <t>På gammal gran (ca 200 år) i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6500,14 +6512,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130719350</v>
+        <v>130839417</v>
       </c>
       <c r="B52" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -6528,29 +6540,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445746</v>
+        <v>445781</v>
       </c>
       <c r="R52" t="n">
-        <v>7026368</v>
+        <v>7026373</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6574,27 +6577,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Draperat på 200-årig gammal levande gran i gammal granskog, längsta bål 60 cm</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6605,21 +6608,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6636,32 +6624,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130839076</v>
+        <v>130300852</v>
       </c>
       <c r="B53" t="n">
-        <v>78256</v>
+        <v>75300</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>6428</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6671,10 +6659,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445706</v>
+        <v>445737</v>
       </c>
       <c r="R53" t="n">
-        <v>7026203</v>
+        <v>7026346</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6701,27 +6689,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6748,32 +6736,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130839080</v>
+        <v>130837541</v>
       </c>
       <c r="B54" t="n">
-        <v>79244</v>
+        <v>75300</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6783,13 +6771,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445706</v>
+        <v>445740</v>
       </c>
       <c r="R54" t="n">
-        <v>7026203</v>
+        <v>7026322</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6818,7 +6806,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6828,12 +6816,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På gammal gran i gles gammal granskog</t>
+          <t>På tunna kvistar vid basen på gammal levande gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6860,10 +6848,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130838040</v>
+        <v>130301741</v>
       </c>
       <c r="B55" t="n">
-        <v>83229</v>
+        <v>83307</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6871,21 +6859,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6895,10 +6883,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445709</v>
+        <v>445718</v>
       </c>
       <c r="R55" t="n">
-        <v>7026357</v>
+        <v>7026281</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6925,27 +6913,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På död gren i hålighet vid basen av gammal levande grov gran (42 cm dbh) i gammal granskog</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6960,22 +6948,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130838768</v>
+        <v>130302583</v>
       </c>
       <c r="B56" t="n">
-        <v>79244</v>
+        <v>83307</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6983,21 +6971,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7007,10 +6995,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445697</v>
+        <v>445687</v>
       </c>
       <c r="R56" t="n">
-        <v>7026283</v>
+        <v>7026235</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7037,27 +7025,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7084,10 +7072,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130838099</v>
+        <v>130837316</v>
       </c>
       <c r="B57" t="n">
-        <v>79244</v>
+        <v>83307</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7095,21 +7083,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7119,10 +7107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445679</v>
+        <v>445777</v>
       </c>
       <c r="R57" t="n">
-        <v>7026381</v>
+        <v>7026331</v>
       </c>
       <c r="S57" t="n">
         <v>6</v>
@@ -7154,7 +7142,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7164,12 +7152,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På död gammal gran</t>
+          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7196,10 +7184,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130838346</v>
+        <v>130837548</v>
       </c>
       <c r="B58" t="n">
-        <v>91829</v>
+        <v>83307</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7207,19 +7195,23 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7227,13 +7219,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445675</v>
+        <v>445740</v>
       </c>
       <c r="R58" t="n">
-        <v>7026326</v>
+        <v>7026322</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7262,7 +7254,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7272,12 +7264,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På levande gran i björkrik granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7304,10 +7296,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130838225</v>
+        <v>130838158</v>
       </c>
       <c r="B59" t="n">
-        <v>79244</v>
+        <v>83307</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7315,21 +7307,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7339,10 +7331,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445632</v>
+        <v>445638</v>
       </c>
       <c r="R59" t="n">
-        <v>7026388</v>
+        <v>7026382</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7374,7 +7366,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7384,12 +7376,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gammal gran i gles skog nära källa</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog, nära källa</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7416,10 +7408,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130839371</v>
+        <v>130839071</v>
       </c>
       <c r="B60" t="n">
-        <v>79244</v>
+        <v>83307</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7427,43 +7419,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445780</v>
+        <v>445706</v>
       </c>
       <c r="R60" t="n">
-        <v>7026357</v>
+        <v>7026203</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7495,7 +7478,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7505,12 +7488,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 200 år) i gles gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7537,10 +7520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130839417</v>
+        <v>130839401</v>
       </c>
       <c r="B61" t="n">
-        <v>79244</v>
+        <v>83307</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7548,21 +7531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7622,7 +7605,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7649,10 +7632,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130838554</v>
+        <v>130301690</v>
       </c>
       <c r="B62" t="n">
-        <v>79244</v>
+        <v>80432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7660,21 +7643,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7684,10 +7667,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445665</v>
+        <v>445682</v>
       </c>
       <c r="R62" t="n">
-        <v>7026277</v>
+        <v>7026217</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7714,27 +7697,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På gammal levande gran i björkrik granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7745,6 +7728,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7754,17 +7752,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130837289</v>
+        <v>130301915</v>
       </c>
       <c r="B63" t="n">
-        <v>79244</v>
+        <v>80432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7772,46 +7770,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445777</v>
+        <v>445762</v>
       </c>
       <c r="R63" t="n">
-        <v>7026331</v>
+        <v>7026257</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7835,27 +7824,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran i gammal granskog</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7870,44 +7859,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, August Nordin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130837438</v>
+        <v>130839069</v>
       </c>
       <c r="B64" t="n">
-        <v>78256</v>
+        <v>79583</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228579</v>
+        <v>6459</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7917,13 +7906,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445741</v>
+        <v>445706</v>
       </c>
       <c r="R64" t="n">
-        <v>7026328</v>
+        <v>7026203</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7952,7 +7941,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7962,12 +7951,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På död gren på gammal levande gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7994,32 +7983,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130837548</v>
+        <v>130301523</v>
       </c>
       <c r="B65" t="n">
-        <v>83224</v>
+        <v>80460</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8029,13 +8018,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445740</v>
+        <v>445674</v>
       </c>
       <c r="R65" t="n">
-        <v>7026322</v>
+        <v>7026247</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8059,27 +8048,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8099,39 +8088,39 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Emil Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130839350</v>
+        <v>130301748</v>
       </c>
       <c r="B66" t="n">
-        <v>79244</v>
+        <v>80461</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8141,13 +8130,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445790</v>
+        <v>445681</v>
       </c>
       <c r="R66" t="n">
-        <v>7026340</v>
+        <v>7026210</v>
       </c>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8171,27 +8160,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8211,17 +8200,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130837393</v>
+        <v>131074382</v>
       </c>
       <c r="B67" t="n">
-        <v>79244</v>
+        <v>58057</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8229,31 +8218,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8262,13 +8251,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445769</v>
+        <v>445791</v>
       </c>
       <c r="R67" t="n">
-        <v>7026332</v>
+        <v>7026340</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8292,27 +8281,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Rikligt på gammal levande gran (ca 175 år, 25 cm dbh) i gammal granskog, längsta bål 40 cm</t>
+          <t>Lockade i ca 3 minuter på en grantopp</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8327,54 +8316,59 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130839110</v>
+        <v>130303489</v>
       </c>
       <c r="B68" t="n">
-        <v>79244</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8383,13 +8377,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445730</v>
+        <v>445824</v>
       </c>
       <c r="R68" t="n">
-        <v>7026205</v>
+        <v>7026381</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8413,27 +8407,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gammal klen död gran i gammal granskog</t>
+          <t>3 vinterståndare på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8453,55 +8447,69 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130837316</v>
+        <v>130303691</v>
       </c>
       <c r="B69" t="n">
-        <v>83224</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445777</v>
+        <v>445781</v>
       </c>
       <c r="R69" t="n">
-        <v>7026331</v>
+        <v>7026394</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8525,27 +8533,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Rikligt på bark på stam av levande gammal gran i gammal granskog</t>
+          <t>5 plantor varav 1 med vinterståndare i gammal granskog, ca 150-200 år.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8565,55 +8573,69 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130838077</v>
+        <v>130303722</v>
       </c>
       <c r="B70" t="n">
-        <v>78256</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445709</v>
+        <v>445791</v>
       </c>
       <c r="R70" t="n">
-        <v>7026369</v>
+        <v>7026379</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8637,27 +8659,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (ca 200 år, 15 cm dbh) i gammal barrblandskog</t>
+          <t>1 vinterståndare och ett skott på marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8677,39 +8699,39 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130838158</v>
+        <v>130301555</v>
       </c>
       <c r="B71" t="n">
-        <v>83224</v>
+        <v>98030</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>221063</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8719,10 +8741,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445638</v>
+        <v>445699</v>
       </c>
       <c r="R71" t="n">
-        <v>7026382</v>
+        <v>7026231</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8749,27 +8771,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog, nära källa</t>
+          <t>På marken i gammal sumpgranskog</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8789,39 +8811,39 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Emil Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130838918</v>
+        <v>130302646</v>
       </c>
       <c r="B72" t="n">
-        <v>79244</v>
+        <v>98030</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8831,13 +8853,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445653</v>
+        <v>445702</v>
       </c>
       <c r="R72" t="n">
-        <v>7026235</v>
+        <v>7026205</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8861,27 +8883,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gammal levande gran (ca 200 år) i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8908,32 +8930,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130839401</v>
+        <v>130300536</v>
       </c>
       <c r="B73" t="n">
-        <v>83224</v>
+        <v>97983</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8943,13 +8965,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445781</v>
+        <v>445736</v>
       </c>
       <c r="R73" t="n">
         <v>7026373</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8973,27 +8995,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På marken i gammal granskog</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9020,32 +9042,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130839069</v>
+        <v>130302398</v>
       </c>
       <c r="B74" t="n">
-        <v>79500</v>
+        <v>78339</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6459</v>
+        <v>228579</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9055,10 +9077,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445706</v>
+        <v>445681</v>
       </c>
       <c r="R74" t="n">
-        <v>7026203</v>
+        <v>7026315</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9085,27 +9107,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran</t>
+          <t>På bark på stam av levande gammal gran (40 cm dbh, ca 180 år) i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9132,10 +9154,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130839071</v>
+        <v>130303129</v>
       </c>
       <c r="B75" t="n">
-        <v>83224</v>
+        <v>78339</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9143,21 +9165,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9167,10 +9189,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445706</v>
+        <v>445734</v>
       </c>
       <c r="R75" t="n">
-        <v>7026203</v>
+        <v>7026229</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9197,27 +9219,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal gransumpskog</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9244,32 +9266,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130837541</v>
+        <v>130303406</v>
       </c>
       <c r="B76" t="n">
-        <v>75222</v>
+        <v>78339</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9279,13 +9301,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445740</v>
+        <v>445827</v>
       </c>
       <c r="R76" t="n">
-        <v>7026322</v>
+        <v>7026371</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9309,27 +9331,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På tunna kvistar vid basen på gammal levande gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9356,10 +9378,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130838833</v>
+        <v>130719785</v>
       </c>
       <c r="B77" t="n">
-        <v>89194</v>
+        <v>78339</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9367,21 +9389,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>228579</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9391,13 +9413,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445685</v>
+        <v>445739</v>
       </c>
       <c r="R77" t="n">
-        <v>7026259</v>
+        <v>7026240</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9421,27 +9443,27 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>På granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9468,10 +9490,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130837733</v>
+        <v>130837438</v>
       </c>
       <c r="B78" t="n">
-        <v>79244</v>
+        <v>78339</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9479,21 +9501,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9503,13 +9525,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445720</v>
+        <v>445741</v>
       </c>
       <c r="R78" t="n">
-        <v>7026343</v>
+        <v>7026328</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9538,7 +9560,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9548,12 +9570,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På gammal död gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9580,10 +9602,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130839413</v>
+        <v>130838077</v>
       </c>
       <c r="B79" t="n">
-        <v>78256</v>
+        <v>78339</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9615,13 +9637,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445781</v>
+        <v>445709</v>
       </c>
       <c r="R79" t="n">
-        <v>7026373</v>
+        <v>7026369</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9650,7 +9672,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9660,12 +9682,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (ca 200 år, 15 cm dbh) i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9692,10 +9714,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130839277</v>
+        <v>130839076</v>
       </c>
       <c r="B80" t="n">
-        <v>79244</v>
+        <v>78339</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9703,46 +9725,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445728</v>
+        <v>445706</v>
       </c>
       <c r="R80" t="n">
-        <v>7026301</v>
+        <v>7026203</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9771,7 +9784,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9781,12 +9794,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9813,57 +9826,48 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131074382</v>
+        <v>130839413</v>
       </c>
       <c r="B81" t="n">
-        <v>57992</v>
+        <v>78339</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Svedaun, Svedaun, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445791</v>
+        <v>445781</v>
       </c>
       <c r="R81" t="n">
-        <v>7026340</v>
+        <v>7026373</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9887,27 +9891,27 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Lockade i ca 3 minuter på en grantopp</t>
+          <t>På bark på stam av levande gammal gran i gles gammal granskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9922,15 +9926,239 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>130300281</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>445810</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7026373</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gren på gammal levande gran i gammal (150+) granskog</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>130303411</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Svedaun, Svedaun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>445827</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7026371</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61201-2025 artfynd.xlsx
+++ b/artfynd/A 61201-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AZ83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303099</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838833</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300541</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719486</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719533</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302241</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302477</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303378</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838040</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1797,6 +1847,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301433</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1909,6 +1964,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301943</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2021,6 +2081,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302348</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300161</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,6 +2310,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300210</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2361,6 +2436,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300326</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2482,6 +2562,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300508</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2603,6 +2688,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300764</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2724,6 +2814,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300940</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2821,6 +2916,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301011</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2942,6 +3042,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301029</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3054,6 +3159,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301089</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3175,6 +3285,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301166</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3296,6 +3411,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301447</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3417,6 +3537,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301787</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3529,6 +3654,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302606</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3641,6 +3771,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302719</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3762,6 +3897,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302963</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3883,6 +4023,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303237</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4004,6 +4149,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303417</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4140,6 +4290,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719248</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4276,6 +4431,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719350</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4388,6 +4548,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719426</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4509,6 +4674,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719742</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4645,6 +4815,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719759</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4766,6 +4941,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719818</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4887,6 +5067,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719892</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5008,6 +5193,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719929</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5129,6 +5319,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130837289</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5250,6 +5445,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130837393</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5362,6 +5562,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130837733</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5474,6 +5679,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838099</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5586,6 +5796,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838225</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5698,6 +5913,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838554</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5810,6 +6030,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838768</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5922,6 +6147,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838918</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6034,6 +6264,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839080</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6155,6 +6390,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839110</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6276,6 +6516,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839277</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6388,6 +6633,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839350</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6509,6 +6759,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839371</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6621,6 +6876,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839417</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6733,6 +6993,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300852</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6845,6 +7110,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130837541</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6957,6 +7227,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301741</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7069,6 +7344,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302583</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7181,6 +7461,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130837316</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7293,6 +7578,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130837548</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7405,6 +7695,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838158</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7517,6 +7812,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839071</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7629,6 +7929,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839401</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7756,6 +8061,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301690</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7868,6 +8178,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301915</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7980,6 +8295,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839069</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8092,6 +8412,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301523</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8204,6 +8529,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301748</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8325,6 +8655,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131074382</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8451,6 +8786,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303489</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8577,6 +8917,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303691</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8703,6 +9048,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303722</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8815,6 +9165,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130301555</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8927,6 +9282,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302646</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9039,6 +9399,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300536</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9151,6 +9516,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130302398</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9263,6 +9633,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303129</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9375,6 +9750,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303406</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9487,6 +9867,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130719785</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9599,6 +9984,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130837438</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9711,6 +10101,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130838077</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9823,6 +10218,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839076</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9935,6 +10335,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130839413</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10047,6 +10452,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130300281</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10159,8 +10569,97 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130303411</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>